--- a/data/dados-turmas-2026.xlsx
+++ b/data/dados-turmas-2026.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arpan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\estatinfo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378A2A44-0936-4FC4-9737-3BF370601AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDC9265-B70D-4257-B66A-22A961E5F4BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="3" r:id="rId1"/>
+    <sheet name="Planilha2" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="55">
   <si>
     <t>Agronomia</t>
   </si>
@@ -138,12 +139,60 @@
   <si>
     <t>consumo_de_alcool</t>
   </si>
+  <si>
+    <t>Não torço</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>São Paulo</t>
+  </si>
+  <si>
+    <t>Palmeiras</t>
+  </si>
+  <si>
+    <t>Corinthians</t>
+  </si>
+  <si>
+    <t>1 a 2 h_sem</t>
+  </si>
+  <si>
+    <t>2 a 2 h_sem</t>
+  </si>
+  <si>
+    <t>3 a 5 h_sem</t>
+  </si>
+  <si>
+    <t>mais de 5 h_sem</t>
+  </si>
+  <si>
+    <t>Mais que social</t>
+  </si>
+  <si>
+    <t>Não informado</t>
+  </si>
+  <si>
+    <t>estudo</t>
+  </si>
+  <si>
+    <t>até 20 h</t>
+  </si>
+  <si>
+    <t>mais 20 h</t>
+  </si>
+  <si>
+    <t>atividade_fisica</t>
+  </si>
+  <si>
+    <t>consumo_alcool</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -157,16 +206,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -174,34 +243,83 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF5B3F86"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF5B3F86"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF5B3F86"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF5B3F86"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -226,13 +344,29 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF5B3F86"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF5B3F86"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF5B3F86"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF5B3F86"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Respostas ao formulário 1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -444,23 +578,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D60CCD58-E5F4-4C6F-A78C-39DF9E1D4064}">
-  <dimension ref="A1:K93"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K92"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="34" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.88671875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
@@ -495,7 +629,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -503,34 +637,34 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
       </c>
       <c r="E2">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F2">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J2" t="s">
         <v>6</v>
       </c>
       <c r="K2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -538,69 +672,69 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
       </c>
       <c r="E3">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H3" t="s">
         <v>9</v>
       </c>
       <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <v>175</v>
+      </c>
+      <c r="F4">
+        <v>18</v>
+      </c>
+      <c r="G4">
         <v>10</v>
-      </c>
-      <c r="J3" t="s">
-        <v>6</v>
-      </c>
-      <c r="K3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>176</v>
-      </c>
-      <c r="F4">
-        <v>18</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
       </c>
       <c r="H4" t="s">
         <v>9</v>
       </c>
       <c r="I4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J4" t="s">
         <v>13</v>
       </c>
       <c r="K4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -608,34 +742,34 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H5" t="s">
         <v>9</v>
       </c>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J5" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -643,19 +777,19 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E6">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H6" t="s">
         <v>9</v>
@@ -667,30 +801,30 @@
         <v>6</v>
       </c>
       <c r="K6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H7" t="s">
         <v>9</v>
@@ -702,10 +836,10 @@
         <v>6</v>
       </c>
       <c r="K7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -713,19 +847,19 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F8">
         <v>19</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H8" t="s">
         <v>9</v>
@@ -734,33 +868,33 @@
         <v>5</v>
       </c>
       <c r="J8" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="K8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E9">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="F9">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H9" t="s">
         <v>9</v>
@@ -769,13 +903,13 @@
         <v>5</v>
       </c>
       <c r="J9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -783,19 +917,19 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G10">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H10" t="s">
         <v>9</v>
@@ -804,33 +938,33 @@
         <v>5</v>
       </c>
       <c r="J10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E11">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F11">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H11" t="s">
         <v>9</v>
@@ -842,15 +976,15 @@
         <v>20</v>
       </c>
       <c r="K11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
         <v>2</v>
@@ -859,63 +993,63 @@
         <v>19</v>
       </c>
       <c r="E12">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="F12">
         <v>18</v>
       </c>
       <c r="G12">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" t="s">
+        <v>5</v>
+      </c>
+      <c r="J12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13">
+        <v>155</v>
+      </c>
+      <c r="F13">
+        <v>20</v>
+      </c>
+      <c r="G13">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
         <v>9</v>
       </c>
-      <c r="I12" t="s">
-        <v>5</v>
-      </c>
-      <c r="J12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13">
-        <v>173</v>
-      </c>
-      <c r="F13">
-        <v>18</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13" t="s">
-        <v>22</v>
-      </c>
       <c r="I13" t="s">
         <v>5</v>
       </c>
       <c r="J13" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -923,19 +1057,19 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
         <v>23</v>
       </c>
       <c r="E14">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G14">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H14" t="s">
         <v>9</v>
@@ -944,13 +1078,13 @@
         <v>5</v>
       </c>
       <c r="J14" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -961,16 +1095,16 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E15">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H15" t="s">
         <v>9</v>
@@ -979,33 +1113,33 @@
         <v>5</v>
       </c>
       <c r="J15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E16">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="F16">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G16">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H16" t="s">
         <v>9</v>
@@ -1014,13 +1148,13 @@
         <v>5</v>
       </c>
       <c r="J16" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="K16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -1028,57 +1162,57 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E17">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="F17">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18">
+        <v>158</v>
+      </c>
+      <c r="F18">
+        <v>19</v>
+      </c>
+      <c r="G18">
+        <v>10</v>
+      </c>
+      <c r="H18" t="s">
         <v>9</v>
-      </c>
-      <c r="I17" t="s">
-        <v>5</v>
-      </c>
-      <c r="J17" t="s">
-        <v>6</v>
-      </c>
-      <c r="K17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18">
-        <v>195</v>
-      </c>
-      <c r="F18">
-        <v>19</v>
-      </c>
-      <c r="G18">
-        <v>7</v>
-      </c>
-      <c r="H18" t="s">
-        <v>22</v>
       </c>
       <c r="I18" t="s">
         <v>5</v>
@@ -1087,65 +1221,65 @@
         <v>13</v>
       </c>
       <c r="K18" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E19">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="F19">
         <v>19</v>
       </c>
       <c r="G19">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H19" t="s">
         <v>9</v>
       </c>
       <c r="I19" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J19" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E20">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="F20">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G20">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H20" t="s">
         <v>9</v>
@@ -1154,13 +1288,13 @@
         <v>10</v>
       </c>
       <c r="J20" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="K20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>0</v>
       </c>
@@ -1174,63 +1308,63 @@
         <v>23</v>
       </c>
       <c r="E21">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="F21">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G21">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H21" t="s">
         <v>9</v>
       </c>
       <c r="I21" t="s">
+        <v>5</v>
+      </c>
+      <c r="J21" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22">
+        <v>170</v>
+      </c>
+      <c r="F22">
+        <v>20</v>
+      </c>
+      <c r="G22">
         <v>10</v>
-      </c>
-      <c r="J21" t="s">
-        <v>6</v>
-      </c>
-      <c r="K21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22">
-        <v>160</v>
-      </c>
-      <c r="F22">
-        <v>18</v>
-      </c>
-      <c r="G22">
-        <v>20</v>
       </c>
       <c r="H22" t="s">
         <v>9</v>
       </c>
       <c r="I22" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>0</v>
       </c>
@@ -1241,31 +1375,31 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E23">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="F23">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G23">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H23" t="s">
         <v>9</v>
       </c>
       <c r="I23" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K23" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -1276,31 +1410,31 @@
         <v>2</v>
       </c>
       <c r="D24" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E24">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H24" t="s">
         <v>9</v>
       </c>
       <c r="I24" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J24" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K24" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>0</v>
       </c>
@@ -1314,98 +1448,98 @@
         <v>23</v>
       </c>
       <c r="E25">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="F25">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H25" t="s">
         <v>9</v>
       </c>
       <c r="I25" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J25" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K25" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E26">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="F26">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H26" t="s">
         <v>9</v>
       </c>
       <c r="I26" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J26" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E27">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="F27">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G27">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H27" t="s">
         <v>9</v>
       </c>
       <c r="I27" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J27" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K27" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>0</v>
       </c>
@@ -1413,104 +1547,104 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E28">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="F28">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H28" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I28" t="s">
         <v>5</v>
       </c>
       <c r="J28" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K28" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E29">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="F29">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H29" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="I29" t="s">
         <v>5</v>
       </c>
       <c r="J29" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K29" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C30" t="s">
         <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E30">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="F30">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G30">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H30" t="s">
         <v>9</v>
       </c>
       <c r="I30" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K30" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>0</v>
       </c>
@@ -1521,22 +1655,22 @@
         <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E31">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="F31">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G31">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H31" t="s">
         <v>9</v>
       </c>
       <c r="I31" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J31" t="s">
         <v>20</v>
@@ -1545,77 +1679,77 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32">
+        <v>161</v>
+      </c>
+      <c r="F32">
+        <v>19</v>
+      </c>
+      <c r="G32">
         <v>15</v>
-      </c>
-      <c r="D32" t="s">
-        <v>23</v>
-      </c>
-      <c r="E32">
-        <v>176</v>
-      </c>
-      <c r="F32">
-        <v>20</v>
-      </c>
-      <c r="G32">
-        <v>9</v>
       </c>
       <c r="H32" t="s">
         <v>9</v>
       </c>
       <c r="I32" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J32" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K32" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C33" t="s">
         <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E33">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="F33">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G33">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H33" t="s">
         <v>9</v>
       </c>
       <c r="I33" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J33" t="s">
         <v>13</v>
       </c>
       <c r="K33" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>0</v>
       </c>
@@ -1626,16 +1760,16 @@
         <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E34">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F34">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G34">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H34" t="s">
         <v>9</v>
@@ -1647,10 +1781,10 @@
         <v>13</v>
       </c>
       <c r="K34" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -1661,31 +1795,31 @@
         <v>2</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E35">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F35">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G35">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H35" t="s">
         <v>9</v>
       </c>
       <c r="I35" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J35" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K35" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -1693,54 +1827,54 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E36">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="F36">
         <v>19</v>
       </c>
       <c r="G36">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H36" t="s">
         <v>9</v>
       </c>
       <c r="I36" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J36" t="s">
+        <v>21</v>
+      </c>
+      <c r="K36" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37">
+        <v>170</v>
+      </c>
+      <c r="F37">
         <v>20</v>
       </c>
-      <c r="K36" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B37" t="s">
-        <v>1</v>
-      </c>
-      <c r="C37" t="s">
-        <v>15</v>
-      </c>
-      <c r="D37" t="s">
-        <v>23</v>
-      </c>
-      <c r="E37">
-        <v>171</v>
-      </c>
-      <c r="F37">
-        <v>19</v>
-      </c>
       <c r="G37">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H37" t="s">
         <v>9</v>
@@ -1749,13 +1883,13 @@
         <v>5</v>
       </c>
       <c r="J37" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K37" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>0</v>
       </c>
@@ -1763,19 +1897,19 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E38">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="F38">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H38" t="s">
         <v>9</v>
@@ -1790,7 +1924,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>0</v>
       </c>
@@ -1798,19 +1932,19 @@
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E39">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="F39">
         <v>19</v>
       </c>
       <c r="G39">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H39" t="s">
         <v>9</v>
@@ -1819,13 +1953,13 @@
         <v>5</v>
       </c>
       <c r="J39" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K39" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>0</v>
       </c>
@@ -1833,104 +1967,104 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D40" t="s">
         <v>24</v>
       </c>
       <c r="E40">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F40">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H40" t="s">
         <v>9</v>
       </c>
       <c r="I40" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J40" t="s">
         <v>6</v>
       </c>
       <c r="K40" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C41" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E41">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="F41">
+        <v>19</v>
+      </c>
+      <c r="G41">
+        <v>10</v>
+      </c>
+      <c r="H41" t="s">
         <v>22</v>
       </c>
-      <c r="G41">
-        <v>9</v>
-      </c>
-      <c r="H41" t="s">
-        <v>9</v>
-      </c>
       <c r="I41" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J41" t="s">
         <v>6</v>
       </c>
       <c r="K41" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D42" t="s">
         <v>23</v>
       </c>
       <c r="E42">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="F42">
         <v>19</v>
       </c>
       <c r="G42">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H42" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="I42" t="s">
         <v>5</v>
       </c>
       <c r="J42" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K42" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>0</v>
       </c>
@@ -1938,19 +2072,19 @@
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E43">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="F43">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G43">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H43" t="s">
         <v>9</v>
@@ -1962,45 +2096,45 @@
         <v>13</v>
       </c>
       <c r="K43" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C44" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D44" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E44">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="F44">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G44">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H44" t="s">
         <v>9</v>
       </c>
       <c r="I44" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J44" t="s">
         <v>13</v>
       </c>
       <c r="K44" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>0</v>
       </c>
@@ -2008,19 +2142,19 @@
         <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D45" t="s">
         <v>3</v>
       </c>
       <c r="E45">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F45">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G45">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H45" t="s">
         <v>9</v>
@@ -2029,68 +2163,68 @@
         <v>10</v>
       </c>
       <c r="J45" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K45" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C46" t="s">
+        <v>2</v>
+      </c>
+      <c r="D46" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46">
+        <v>176</v>
+      </c>
+      <c r="F46">
+        <v>19</v>
+      </c>
+      <c r="G46">
         <v>8</v>
-      </c>
-      <c r="D46" t="s">
-        <v>3</v>
-      </c>
-      <c r="E46">
-        <v>159</v>
-      </c>
-      <c r="F46">
-        <v>19</v>
-      </c>
-      <c r="G46">
-        <v>6</v>
       </c>
       <c r="H46" t="s">
         <v>9</v>
       </c>
       <c r="I46" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J46" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K46" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C47" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D47" t="s">
         <v>24</v>
       </c>
       <c r="E47">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="F47">
         <v>19</v>
       </c>
       <c r="G47">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H47" t="s">
         <v>9</v>
@@ -2099,33 +2233,33 @@
         <v>5</v>
       </c>
       <c r="J47" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K47" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C48" t="s">
         <v>8</v>
       </c>
       <c r="D48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E48">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="F48">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G48">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H48" t="s">
         <v>9</v>
@@ -2134,144 +2268,144 @@
         <v>5</v>
       </c>
       <c r="J48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2</v>
+      </c>
+      <c r="D49" t="s">
+        <v>3</v>
+      </c>
+      <c r="E49">
+        <v>164</v>
+      </c>
+      <c r="F49">
+        <v>19</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+      <c r="H49" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" t="s">
+        <v>10</v>
+      </c>
+      <c r="J49" t="s">
+        <v>6</v>
+      </c>
+      <c r="K49" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>0</v>
-      </c>
-      <c r="B49" t="s">
-        <v>1</v>
-      </c>
-      <c r="C49" t="s">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" t="s">
         <v>8</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D50" t="s">
         <v>23</v>
       </c>
-      <c r="E49">
-        <v>183</v>
-      </c>
-      <c r="F49">
-        <v>21</v>
-      </c>
-      <c r="G49">
-        <v>3</v>
-      </c>
-      <c r="H49" t="s">
+      <c r="E50">
+        <v>160</v>
+      </c>
+      <c r="F50">
+        <v>19</v>
+      </c>
+      <c r="G50">
+        <v>6</v>
+      </c>
+      <c r="H50" t="s">
         <v>9</v>
       </c>
-      <c r="I49" t="s">
-        <v>5</v>
-      </c>
-      <c r="J49" t="s">
-        <v>21</v>
-      </c>
-      <c r="K49" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>0</v>
-      </c>
-      <c r="B50" t="s">
-        <v>18</v>
-      </c>
-      <c r="C50" t="s">
-        <v>2</v>
-      </c>
-      <c r="D50" t="s">
-        <v>3</v>
-      </c>
-      <c r="E50">
-        <v>164</v>
-      </c>
-      <c r="F50">
-        <v>19</v>
-      </c>
-      <c r="G50">
-        <v>2</v>
-      </c>
-      <c r="H50" t="s">
-        <v>22</v>
-      </c>
       <c r="I50" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J50" t="s">
         <v>6</v>
       </c>
       <c r="K50" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>2</v>
+      </c>
+      <c r="D51" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51">
+        <v>182</v>
+      </c>
+      <c r="F51">
+        <v>18</v>
+      </c>
+      <c r="G51">
+        <v>18</v>
+      </c>
+      <c r="H51" t="s">
+        <v>26</v>
+      </c>
+      <c r="I51" t="s">
+        <v>10</v>
+      </c>
+      <c r="J51" t="s">
+        <v>13</v>
+      </c>
+      <c r="K51" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>0</v>
-      </c>
-      <c r="B51" t="s">
-        <v>18</v>
-      </c>
-      <c r="C51" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" t="s">
-        <v>23</v>
-      </c>
-      <c r="E51">
-        <v>160</v>
-      </c>
-      <c r="F51">
-        <v>19</v>
-      </c>
-      <c r="G51">
-        <v>6</v>
-      </c>
-      <c r="H51" t="s">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>0</v>
+      </c>
+      <c r="B52" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52">
+        <v>165</v>
+      </c>
+      <c r="F52">
+        <v>19</v>
+      </c>
+      <c r="G52">
+        <v>3</v>
+      </c>
+      <c r="H52" t="s">
         <v>9</v>
       </c>
-      <c r="I51" t="s">
-        <v>5</v>
-      </c>
-      <c r="J51" t="s">
-        <v>6</v>
-      </c>
-      <c r="K51" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>0</v>
-      </c>
-      <c r="B52" t="s">
-        <v>1</v>
-      </c>
-      <c r="C52" t="s">
-        <v>2</v>
-      </c>
-      <c r="D52" t="s">
-        <v>24</v>
-      </c>
-      <c r="E52">
-        <v>182</v>
-      </c>
-      <c r="F52">
-        <v>18</v>
-      </c>
-      <c r="G52">
-        <v>18</v>
-      </c>
-      <c r="H52" t="s">
-        <v>26</v>
-      </c>
       <c r="I52" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J52" t="s">
         <v>13</v>
@@ -2280,42 +2414,42 @@
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>0</v>
       </c>
       <c r="B53" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D53" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E53">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="F53">
         <v>19</v>
       </c>
       <c r="G53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H53" t="s">
         <v>9</v>
       </c>
       <c r="I53" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J53" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K53" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>0</v>
       </c>
@@ -2323,34 +2457,34 @@
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D54" t="s">
         <v>3</v>
       </c>
       <c r="E54">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="F54">
         <v>19</v>
       </c>
       <c r="G54">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H54" t="s">
         <v>9</v>
       </c>
       <c r="I54" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J54" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K54" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>0</v>
       </c>
@@ -2358,19 +2492,19 @@
         <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D55" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E55">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="F55">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H55" t="s">
         <v>9</v>
@@ -2382,10 +2516,10 @@
         <v>13</v>
       </c>
       <c r="K55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>0</v>
       </c>
@@ -2396,16 +2530,16 @@
         <v>2</v>
       </c>
       <c r="D56" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E56">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="F56">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H56" t="s">
         <v>9</v>
@@ -2414,13 +2548,13 @@
         <v>5</v>
       </c>
       <c r="J56" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K56" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>0</v>
       </c>
@@ -2428,19 +2562,19 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D57" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E57">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F57">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G57">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H57" t="s">
         <v>9</v>
@@ -2449,13 +2583,13 @@
         <v>5</v>
       </c>
       <c r="J57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K57" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>0</v>
       </c>
@@ -2463,19 +2597,19 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D58" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E58">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="F58">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H58" t="s">
         <v>9</v>
@@ -2490,7 +2624,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>0</v>
       </c>
@@ -2498,19 +2632,19 @@
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D59" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E59">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="F59">
         <v>19</v>
       </c>
       <c r="G59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H59" t="s">
         <v>9</v>
@@ -2519,13 +2653,13 @@
         <v>5</v>
       </c>
       <c r="J59" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K59" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>0</v>
       </c>
@@ -2536,16 +2670,16 @@
         <v>2</v>
       </c>
       <c r="D60" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E60">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F60">
         <v>19</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H60" t="s">
         <v>9</v>
@@ -2560,7 +2694,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>0</v>
       </c>
@@ -2571,16 +2705,16 @@
         <v>2</v>
       </c>
       <c r="D61" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61">
+        <v>175</v>
+      </c>
+      <c r="F61">
+        <v>19</v>
+      </c>
+      <c r="G61">
         <v>3</v>
-      </c>
-      <c r="E61">
-        <v>174</v>
-      </c>
-      <c r="F61">
-        <v>19</v>
-      </c>
-      <c r="G61">
-        <v>8</v>
       </c>
       <c r="H61" t="s">
         <v>9</v>
@@ -2595,7 +2729,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>0</v>
       </c>
@@ -2603,16 +2737,16 @@
         <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D62" t="s">
         <v>24</v>
       </c>
       <c r="E62">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F62">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G62">
         <v>3</v>
@@ -2630,7 +2764,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>0</v>
       </c>
@@ -2638,16 +2772,16 @@
         <v>1</v>
       </c>
       <c r="C63" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D63" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E63">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F63">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G63">
         <v>3</v>
@@ -2659,13 +2793,13 @@
         <v>5</v>
       </c>
       <c r="J63" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K63" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>0</v>
       </c>
@@ -2673,19 +2807,19 @@
         <v>1</v>
       </c>
       <c r="C64" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D64" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E64">
         <v>170</v>
       </c>
       <c r="F64">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H64" t="s">
         <v>9</v>
@@ -2694,13 +2828,13 @@
         <v>5</v>
       </c>
       <c r="J64" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="K64" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>0</v>
       </c>
@@ -2711,16 +2845,16 @@
         <v>15</v>
       </c>
       <c r="D65" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E65">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="F65">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H65" t="s">
         <v>9</v>
@@ -2729,13 +2863,13 @@
         <v>5</v>
       </c>
       <c r="J65" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K65" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>0</v>
       </c>
@@ -2743,19 +2877,19 @@
         <v>1</v>
       </c>
       <c r="C66" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D66" t="s">
         <v>23</v>
       </c>
       <c r="E66">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F66">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G66">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H66" t="s">
         <v>9</v>
@@ -2764,18 +2898,18 @@
         <v>5</v>
       </c>
       <c r="J66" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K66" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B67" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C67" t="s">
         <v>2</v>
@@ -2784,28 +2918,28 @@
         <v>23</v>
       </c>
       <c r="E67">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F67">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G67">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H67" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I67" t="s">
         <v>5</v>
       </c>
       <c r="J67" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K67" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>27</v>
       </c>
@@ -2813,104 +2947,104 @@
         <v>18</v>
       </c>
       <c r="C68" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E68">
+        <v>164</v>
+      </c>
+      <c r="F68">
         <v>23</v>
       </c>
-      <c r="E68">
-        <v>172</v>
-      </c>
-      <c r="F68">
-        <v>26</v>
-      </c>
       <c r="G68">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H68" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I68" t="s">
         <v>5</v>
       </c>
       <c r="J68" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K68" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>27</v>
       </c>
       <c r="B69" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C69" t="s">
         <v>15</v>
       </c>
       <c r="D69" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E69">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="F69">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H69" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I69" t="s">
         <v>5</v>
       </c>
       <c r="J69" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K69" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>27</v>
       </c>
       <c r="B70" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C70" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D70" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E70">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="F70">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G70">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H70" t="s">
         <v>4</v>
       </c>
       <c r="I70" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J70" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K70" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>27</v>
       </c>
@@ -2921,31 +3055,31 @@
         <v>2</v>
       </c>
       <c r="D71" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E71">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="F71">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G71">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H71" t="s">
         <v>4</v>
       </c>
       <c r="I71" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J71" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K71" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>27</v>
       </c>
@@ -2956,31 +3090,31 @@
         <v>2</v>
       </c>
       <c r="D72" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E72">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F72">
         <v>19</v>
       </c>
       <c r="G72">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H72" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I72" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J72" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K72" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>27</v>
       </c>
@@ -2994,63 +3128,63 @@
         <v>23</v>
       </c>
       <c r="E73">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="F73">
         <v>19</v>
       </c>
       <c r="G73">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H73" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I73" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J73" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K73" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>27</v>
       </c>
       <c r="B74" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C74" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D74" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E74">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F74">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G74">
+        <v>6</v>
+      </c>
+      <c r="H74" t="s">
+        <v>9</v>
+      </c>
+      <c r="I74" t="s">
         <v>10</v>
       </c>
-      <c r="H74" t="s">
-        <v>4</v>
-      </c>
-      <c r="I74" t="s">
-        <v>5</v>
-      </c>
       <c r="J74" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K74" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>27</v>
       </c>
@@ -3061,51 +3195,51 @@
         <v>8</v>
       </c>
       <c r="D75" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E75">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="F75">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G75">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H75" t="s">
         <v>9</v>
       </c>
       <c r="I75" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J75" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K75" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>27</v>
       </c>
       <c r="B76" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C76" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E76">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="F76">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G76">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H76" t="s">
         <v>9</v>
@@ -3117,10 +3251,10 @@
         <v>13</v>
       </c>
       <c r="K76" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>27</v>
       </c>
@@ -3128,54 +3262,54 @@
         <v>18</v>
       </c>
       <c r="C77" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D77" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E77">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="F77">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G77">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H77" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I77" t="s">
         <v>5</v>
       </c>
       <c r="J77" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K77" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>27</v>
       </c>
       <c r="B78" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C78" t="s">
         <v>2</v>
       </c>
       <c r="D78" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E78">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F78">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G78">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H78" t="s">
         <v>4</v>
@@ -3184,13 +3318,13 @@
         <v>5</v>
       </c>
       <c r="J78" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K78" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>27</v>
       </c>
@@ -3198,34 +3332,34 @@
         <v>1</v>
       </c>
       <c r="C79" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D79" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E79">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F79">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G79">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H79" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I79" t="s">
         <v>5</v>
       </c>
       <c r="J79" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K79" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>27</v>
       </c>
@@ -3233,54 +3367,54 @@
         <v>1</v>
       </c>
       <c r="C80" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D80" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E80">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F80">
+        <v>38</v>
+      </c>
+      <c r="G80">
+        <v>2</v>
+      </c>
+      <c r="H80" t="s">
+        <v>4</v>
+      </c>
+      <c r="I80" t="s">
+        <v>5</v>
+      </c>
+      <c r="J80" t="s">
         <v>20</v>
       </c>
-      <c r="G80">
-        <v>5</v>
-      </c>
-      <c r="H80" t="s">
-        <v>9</v>
-      </c>
-      <c r="I80" t="s">
-        <v>5</v>
-      </c>
-      <c r="J80" t="s">
-        <v>13</v>
-      </c>
       <c r="K80" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>27</v>
       </c>
       <c r="B81" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C81" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D81" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E81">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F81">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="G81">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H81" t="s">
         <v>4</v>
@@ -3292,10 +3426,10 @@
         <v>20</v>
       </c>
       <c r="K81" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>27</v>
       </c>
@@ -3303,19 +3437,19 @@
         <v>18</v>
       </c>
       <c r="C82" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D82" t="s">
         <v>23</v>
       </c>
       <c r="E82">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="F82">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G82">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H82" t="s">
         <v>4</v>
@@ -3327,10 +3461,10 @@
         <v>20</v>
       </c>
       <c r="K82" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>27</v>
       </c>
@@ -3338,39 +3472,39 @@
         <v>18</v>
       </c>
       <c r="C83" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D83" t="s">
         <v>23</v>
       </c>
       <c r="E83">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F83">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G83">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H83" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I83" t="s">
         <v>5</v>
       </c>
       <c r="J83" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K83" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C84" t="s">
         <v>2</v>
@@ -3382,25 +3516,25 @@
         <v>170</v>
       </c>
       <c r="F84">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G84">
+        <v>6</v>
+      </c>
+      <c r="H84" t="s">
         <v>4</v>
       </c>
-      <c r="H84" t="s">
-        <v>9</v>
-      </c>
       <c r="I84" t="s">
         <v>5</v>
       </c>
       <c r="J84" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="K84" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>27</v>
       </c>
@@ -3411,19 +3545,19 @@
         <v>2</v>
       </c>
       <c r="D85" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E85">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="F85">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G85">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H85" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I85" t="s">
         <v>5</v>
@@ -3432,45 +3566,45 @@
         <v>21</v>
       </c>
       <c r="K85" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>27</v>
       </c>
       <c r="B86" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C86" t="s">
         <v>2</v>
       </c>
       <c r="D86" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E86">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F86">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G86">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H86" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I86" t="s">
         <v>5</v>
       </c>
       <c r="J86" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="K86" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>27</v>
       </c>
@@ -3478,19 +3612,19 @@
         <v>18</v>
       </c>
       <c r="C87" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D87" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E87">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F87">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G87">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H87" t="s">
         <v>4</v>
@@ -3499,36 +3633,36 @@
         <v>5</v>
       </c>
       <c r="J87" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="K87" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>27</v>
       </c>
       <c r="B88" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C88" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D88" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E88">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="F88">
         <v>19</v>
       </c>
       <c r="G88">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H88" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="I88" t="s">
         <v>5</v>
@@ -3540,7 +3674,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>27</v>
       </c>
@@ -3548,34 +3682,34 @@
         <v>1</v>
       </c>
       <c r="C89" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D89" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E89">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="F89">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G89">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H89" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I89" t="s">
         <v>5</v>
       </c>
       <c r="J89" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K89" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>27</v>
       </c>
@@ -3583,19 +3717,19 @@
         <v>1</v>
       </c>
       <c r="C90" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D90" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E90">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F90">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G90">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H90" t="s">
         <v>4</v>
@@ -3610,7 +3744,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>27</v>
       </c>
@@ -3618,19 +3752,19 @@
         <v>1</v>
       </c>
       <c r="C91" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D91" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E91">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="F91">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G91">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H91" t="s">
         <v>4</v>
@@ -3639,33 +3773,33 @@
         <v>5</v>
       </c>
       <c r="J91" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K91" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>27</v>
       </c>
       <c r="B92" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C92" t="s">
         <v>2</v>
       </c>
       <c r="D92" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E92">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F92">
         <v>19</v>
       </c>
       <c r="G92">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H92" t="s">
         <v>4</v>
@@ -3674,48 +3808,3548 @@
         <v>5</v>
       </c>
       <c r="J92" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K92" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
-        <v>27</v>
-      </c>
-      <c r="B93" t="s">
-        <v>18</v>
-      </c>
-      <c r="C93" t="s">
-        <v>2</v>
-      </c>
-      <c r="D93" t="s">
-        <v>3</v>
-      </c>
-      <c r="E93">
-        <v>165</v>
-      </c>
-      <c r="F93">
-        <v>19</v>
-      </c>
-      <c r="G93">
-        <v>5</v>
-      </c>
-      <c r="H93" t="s">
-        <v>4</v>
-      </c>
-      <c r="I93" t="s">
-        <v>5</v>
-      </c>
-      <c r="J93" t="s">
-        <v>13</v>
-      </c>
-      <c r="K93" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67291CED-4854-4A07-9C00-39F7F3C0BA26}">
+  <dimension ref="A1:X92"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="1.88671875" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="6" max="6" width="3" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3" customWidth="1"/>
+    <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3" customWidth="1"/>
+    <col min="13" max="13" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="3" customWidth="1"/>
+    <col min="15" max="15" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="3" customWidth="1"/>
+    <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3" customWidth="1"/>
+    <col min="20" max="20" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3" customWidth="1"/>
+    <col min="22" max="22" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.44140625" customWidth="1"/>
+    <col min="24" max="24" width="16.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C1" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="R1" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="T1" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="V1" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="X1" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="8">
+        <v>155</v>
+      </c>
+      <c r="M2" s="2">
+        <v>18</v>
+      </c>
+      <c r="O2" s="8">
+        <v>0</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="V2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="X2" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" s="9">
+        <v>155</v>
+      </c>
+      <c r="M3" s="3">
+        <v>18</v>
+      </c>
+      <c r="O3" s="9">
+        <v>1</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="X3" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" s="9">
+        <v>155</v>
+      </c>
+      <c r="M4" s="3">
+        <v>18</v>
+      </c>
+      <c r="O4" s="9">
+        <v>1</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="X4" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="9">
+        <v>157</v>
+      </c>
+      <c r="M5" s="3">
+        <v>18</v>
+      </c>
+      <c r="O5" s="9">
+        <v>2</v>
+      </c>
+      <c r="R5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="X5" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="9">
+        <v>158</v>
+      </c>
+      <c r="M6" s="3">
+        <v>18</v>
+      </c>
+      <c r="O6" s="9">
+        <v>2</v>
+      </c>
+      <c r="R6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="X6" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="9">
+        <v>159</v>
+      </c>
+      <c r="M7" s="3">
+        <v>18</v>
+      </c>
+      <c r="O7" s="9">
+        <v>2</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="X7" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" s="9">
+        <v>160</v>
+      </c>
+      <c r="M8" s="3">
+        <v>18</v>
+      </c>
+      <c r="O8" s="9">
+        <v>2</v>
+      </c>
+      <c r="R8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T8" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V8" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="X8" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="9">
+        <v>160</v>
+      </c>
+      <c r="M9" s="3">
+        <v>18</v>
+      </c>
+      <c r="O9" s="9">
+        <v>2</v>
+      </c>
+      <c r="R9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="X9" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10" s="9">
+        <v>160</v>
+      </c>
+      <c r="M10" s="3">
+        <v>18</v>
+      </c>
+      <c r="O10" s="9">
+        <v>2</v>
+      </c>
+      <c r="R10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="X10" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K11" s="9">
+        <v>160</v>
+      </c>
+      <c r="M11" s="3">
+        <v>18</v>
+      </c>
+      <c r="O11" s="9">
+        <v>2</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T11" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V11" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="X11" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12" s="9">
+        <v>160</v>
+      </c>
+      <c r="M12" s="3">
+        <v>18</v>
+      </c>
+      <c r="O12" s="9">
+        <v>2</v>
+      </c>
+      <c r="R12" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T12" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V12" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="X12" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K13" s="9">
+        <v>161</v>
+      </c>
+      <c r="M13" s="3">
+        <v>18</v>
+      </c>
+      <c r="O13" s="9">
+        <v>3</v>
+      </c>
+      <c r="R13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T13" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="X13" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K14" s="9">
+        <v>161</v>
+      </c>
+      <c r="M14" s="3">
+        <v>18</v>
+      </c>
+      <c r="O14" s="9">
+        <v>3</v>
+      </c>
+      <c r="R14" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="X14" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K15" s="9">
+        <v>162</v>
+      </c>
+      <c r="M15" s="3">
+        <v>18</v>
+      </c>
+      <c r="O15" s="9">
+        <v>3</v>
+      </c>
+      <c r="R15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T15" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="X15" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K16" s="9">
+        <v>162</v>
+      </c>
+      <c r="M16" s="3">
+        <v>18</v>
+      </c>
+      <c r="O16" s="9">
+        <v>3</v>
+      </c>
+      <c r="R16" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="X16" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K17" s="9">
+        <v>163</v>
+      </c>
+      <c r="M17" s="3">
+        <v>18</v>
+      </c>
+      <c r="O17" s="9">
+        <v>3</v>
+      </c>
+      <c r="R17" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T17" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="X17" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K18" s="9">
+        <v>163</v>
+      </c>
+      <c r="M18" s="3">
+        <v>18</v>
+      </c>
+      <c r="O18" s="9">
+        <v>3</v>
+      </c>
+      <c r="R18" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V18" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="X18" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K19" s="9">
+        <v>163</v>
+      </c>
+      <c r="M19" s="3">
+        <v>18</v>
+      </c>
+      <c r="O19" s="9">
+        <v>3</v>
+      </c>
+      <c r="R19" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T19" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V19" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="X19" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K20" s="9">
+        <v>164</v>
+      </c>
+      <c r="M20" s="3">
+        <v>18</v>
+      </c>
+      <c r="O20" s="9">
+        <v>3</v>
+      </c>
+      <c r="R20" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V20" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X20" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K21" s="9">
+        <v>164</v>
+      </c>
+      <c r="M21" s="3">
+        <v>19</v>
+      </c>
+      <c r="O21" s="9">
+        <v>3</v>
+      </c>
+      <c r="R21" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X21" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K22" s="9">
+        <v>164</v>
+      </c>
+      <c r="M22" s="3">
+        <v>19</v>
+      </c>
+      <c r="O22" s="9">
+        <v>3</v>
+      </c>
+      <c r="R22" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T22" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V22" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X22" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K23" s="9">
+        <v>164</v>
+      </c>
+      <c r="M23" s="3">
+        <v>19</v>
+      </c>
+      <c r="O23" s="9">
+        <v>3</v>
+      </c>
+      <c r="R23" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V23" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X23" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K24" s="9">
+        <v>165</v>
+      </c>
+      <c r="M24" s="3">
+        <v>19</v>
+      </c>
+      <c r="O24" s="9">
+        <v>3</v>
+      </c>
+      <c r="R24" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X24" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K25" s="9">
+        <v>165</v>
+      </c>
+      <c r="M25" s="3">
+        <v>19</v>
+      </c>
+      <c r="O25" s="9">
+        <v>4</v>
+      </c>
+      <c r="R25" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T25" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V25" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X25" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K26" s="9">
+        <v>165</v>
+      </c>
+      <c r="M26" s="3">
+        <v>19</v>
+      </c>
+      <c r="O26" s="9">
+        <v>4</v>
+      </c>
+      <c r="R26" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T26" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V26" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X26" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K27" s="9">
+        <v>165</v>
+      </c>
+      <c r="M27" s="3">
+        <v>19</v>
+      </c>
+      <c r="O27" s="9">
+        <v>4</v>
+      </c>
+      <c r="R27" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T27" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V27" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X27" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K28" s="9">
+        <v>167</v>
+      </c>
+      <c r="M28" s="3">
+        <v>19</v>
+      </c>
+      <c r="O28" s="9">
+        <v>4</v>
+      </c>
+      <c r="R28" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T28" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V28" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X28" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K29" s="9">
+        <v>167</v>
+      </c>
+      <c r="M29" s="3">
+        <v>19</v>
+      </c>
+      <c r="O29" s="9">
+        <v>4</v>
+      </c>
+      <c r="R29" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T29" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V29" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X29" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K30" s="9">
+        <v>169</v>
+      </c>
+      <c r="M30" s="3">
+        <v>19</v>
+      </c>
+      <c r="O30" s="9">
+        <v>4</v>
+      </c>
+      <c r="R30" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T30" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V30" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X30" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K31" s="9">
+        <v>170</v>
+      </c>
+      <c r="M31" s="3">
+        <v>19</v>
+      </c>
+      <c r="O31" s="9">
+        <v>4</v>
+      </c>
+      <c r="R31" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T31" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V31" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X31" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K32" s="9">
+        <v>170</v>
+      </c>
+      <c r="M32" s="3">
+        <v>19</v>
+      </c>
+      <c r="O32" s="9">
+        <v>4</v>
+      </c>
+      <c r="R32" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T32" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V32" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X32" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K33" s="9">
+        <v>170</v>
+      </c>
+      <c r="M33" s="3">
+        <v>19</v>
+      </c>
+      <c r="O33" s="9">
+        <v>4</v>
+      </c>
+      <c r="R33" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T33" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V33" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X33" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K34" s="9">
+        <v>170</v>
+      </c>
+      <c r="M34" s="3">
+        <v>19</v>
+      </c>
+      <c r="O34" s="9">
+        <v>5</v>
+      </c>
+      <c r="R34" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T34" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V34" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X34" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K35" s="9">
+        <v>170</v>
+      </c>
+      <c r="M35" s="3">
+        <v>19</v>
+      </c>
+      <c r="O35" s="9">
+        <v>5</v>
+      </c>
+      <c r="R35" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T35" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V35" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X35" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K36" s="9">
+        <v>170</v>
+      </c>
+      <c r="M36" s="3">
+        <v>19</v>
+      </c>
+      <c r="O36" s="9">
+        <v>5</v>
+      </c>
+      <c r="R36" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T36" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V36" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X36" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K37" s="9">
+        <v>170</v>
+      </c>
+      <c r="M37" s="3">
+        <v>19</v>
+      </c>
+      <c r="O37" s="9">
+        <v>5</v>
+      </c>
+      <c r="R37" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T37" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V37" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X37" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K38" s="9">
+        <v>170</v>
+      </c>
+      <c r="M38" s="3">
+        <v>19</v>
+      </c>
+      <c r="O38" s="9">
+        <v>5</v>
+      </c>
+      <c r="R38" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T38" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V38" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X38" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K39" s="9">
+        <v>171</v>
+      </c>
+      <c r="M39" s="3">
+        <v>19</v>
+      </c>
+      <c r="O39" s="9">
+        <v>5</v>
+      </c>
+      <c r="R39" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T39" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V39" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="X39" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K40" s="9">
+        <v>172</v>
+      </c>
+      <c r="M40" s="3">
+        <v>19</v>
+      </c>
+      <c r="O40" s="9">
+        <v>5</v>
+      </c>
+      <c r="R40" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T40" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V40" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X40" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K41" s="9">
+        <v>172</v>
+      </c>
+      <c r="M41" s="3">
+        <v>19</v>
+      </c>
+      <c r="O41" s="9">
+        <v>5</v>
+      </c>
+      <c r="R41" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T41" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V41" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X41" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K42" s="9">
+        <v>172</v>
+      </c>
+      <c r="M42" s="3">
+        <v>19</v>
+      </c>
+      <c r="O42" s="9">
+        <v>5</v>
+      </c>
+      <c r="R42" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T42" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V42" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X42" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K43" s="9">
+        <v>173</v>
+      </c>
+      <c r="M43" s="3">
+        <v>19</v>
+      </c>
+      <c r="O43" s="9">
+        <v>5</v>
+      </c>
+      <c r="R43" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T43" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V43" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X43" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K44" s="9">
+        <v>173</v>
+      </c>
+      <c r="M44" s="3">
+        <v>19</v>
+      </c>
+      <c r="O44" s="9">
+        <v>6</v>
+      </c>
+      <c r="R44" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T44" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V44" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X44" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K45" s="9">
+        <v>173</v>
+      </c>
+      <c r="M45" s="3">
+        <v>19</v>
+      </c>
+      <c r="O45" s="9">
+        <v>6</v>
+      </c>
+      <c r="R45" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T45" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V45" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X45" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K46" s="9">
+        <v>173</v>
+      </c>
+      <c r="M46" s="3">
+        <v>19</v>
+      </c>
+      <c r="O46" s="9">
+        <v>6</v>
+      </c>
+      <c r="R46" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T46" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V46" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X46" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K47" s="9">
+        <v>173</v>
+      </c>
+      <c r="M47" s="3">
+        <v>19</v>
+      </c>
+      <c r="O47" s="9">
+        <v>6</v>
+      </c>
+      <c r="R47" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T47" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V47" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X47" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K48" s="9">
+        <v>173</v>
+      </c>
+      <c r="M48" s="3">
+        <v>19</v>
+      </c>
+      <c r="O48" s="9">
+        <v>6</v>
+      </c>
+      <c r="R48" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T48" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V48" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X48" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K49" s="9">
+        <v>173</v>
+      </c>
+      <c r="M49" s="3">
+        <v>19</v>
+      </c>
+      <c r="O49" s="9">
+        <v>6</v>
+      </c>
+      <c r="R49" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T49" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V49" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X49" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K50" s="9">
+        <v>173</v>
+      </c>
+      <c r="M50" s="3">
+        <v>19</v>
+      </c>
+      <c r="O50" s="9">
+        <v>6</v>
+      </c>
+      <c r="R50" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T50" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V50" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X50" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K51" s="9">
+        <v>174</v>
+      </c>
+      <c r="M51" s="3">
+        <v>19</v>
+      </c>
+      <c r="O51" s="9">
+        <v>6</v>
+      </c>
+      <c r="R51" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T51" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V51" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X51" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K52" s="9">
+        <v>174</v>
+      </c>
+      <c r="M52" s="3">
+        <v>19</v>
+      </c>
+      <c r="O52" s="9">
+        <v>6</v>
+      </c>
+      <c r="R52" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T52" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V52" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X52" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K53" s="9">
+        <v>174</v>
+      </c>
+      <c r="M53" s="3">
+        <v>19</v>
+      </c>
+      <c r="O53" s="9">
+        <v>6</v>
+      </c>
+      <c r="R53" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T53" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V53" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X53" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K54" s="9">
+        <v>175</v>
+      </c>
+      <c r="M54" s="3">
+        <v>19</v>
+      </c>
+      <c r="O54" s="9">
+        <v>6</v>
+      </c>
+      <c r="R54" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T54" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V54" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X54" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K55" s="9">
+        <v>175</v>
+      </c>
+      <c r="M55" s="3">
+        <v>19</v>
+      </c>
+      <c r="O55" s="9">
+        <v>7</v>
+      </c>
+      <c r="R55" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T55" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V55" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X55" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K56" s="9">
+        <v>175</v>
+      </c>
+      <c r="M56" s="3">
+        <v>19</v>
+      </c>
+      <c r="O56" s="9">
+        <v>7</v>
+      </c>
+      <c r="R56" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T56" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V56" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X56" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K57" s="9">
+        <v>175</v>
+      </c>
+      <c r="M57" s="3">
+        <v>19</v>
+      </c>
+      <c r="O57" s="9">
+        <v>8</v>
+      </c>
+      <c r="R57" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T57" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V57" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X57" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K58" s="9">
+        <v>176</v>
+      </c>
+      <c r="M58" s="3">
+        <v>19</v>
+      </c>
+      <c r="O58" s="9">
+        <v>8</v>
+      </c>
+      <c r="R58" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T58" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V58" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X58" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K59" s="9">
+        <v>176</v>
+      </c>
+      <c r="M59" s="3">
+        <v>19</v>
+      </c>
+      <c r="O59" s="9">
+        <v>8</v>
+      </c>
+      <c r="R59" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T59" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V59" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X59" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K60" s="9">
+        <v>176</v>
+      </c>
+      <c r="M60" s="3">
+        <v>19</v>
+      </c>
+      <c r="O60" s="9">
+        <v>8</v>
+      </c>
+      <c r="R60" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T60" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V60" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X60" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K61" s="9">
+        <v>176</v>
+      </c>
+      <c r="M61" s="3">
+        <v>20</v>
+      </c>
+      <c r="O61" s="9">
+        <v>8</v>
+      </c>
+      <c r="R61" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T61" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V61" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X61" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K62" s="9">
+        <v>176</v>
+      </c>
+      <c r="M62" s="3">
+        <v>20</v>
+      </c>
+      <c r="O62" s="9">
+        <v>8</v>
+      </c>
+      <c r="R62" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T62" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V62" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X62" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K63" s="9">
+        <v>176</v>
+      </c>
+      <c r="M63" s="3">
+        <v>20</v>
+      </c>
+      <c r="O63" s="9">
+        <v>8</v>
+      </c>
+      <c r="R63" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T63" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V63" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X63" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K64" s="9">
+        <v>176</v>
+      </c>
+      <c r="M64" s="3">
+        <v>20</v>
+      </c>
+      <c r="O64" s="9">
+        <v>8</v>
+      </c>
+      <c r="R64" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T64" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V64" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X64" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K65" s="9">
+        <v>176</v>
+      </c>
+      <c r="M65" s="3">
+        <v>20</v>
+      </c>
+      <c r="O65" s="9">
+        <v>9</v>
+      </c>
+      <c r="R65" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T65" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V65" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X65" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G66" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K66" s="9">
+        <v>176</v>
+      </c>
+      <c r="M66" s="3">
+        <v>20</v>
+      </c>
+      <c r="O66" s="9">
+        <v>9</v>
+      </c>
+      <c r="R66" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T66" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V66" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X66" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K67" s="9">
+        <v>177</v>
+      </c>
+      <c r="M67" s="3">
+        <v>20</v>
+      </c>
+      <c r="O67" s="9">
+        <v>10</v>
+      </c>
+      <c r="R67" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T67" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V67" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X67" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K68" s="9">
+        <v>177</v>
+      </c>
+      <c r="M68" s="3">
+        <v>20</v>
+      </c>
+      <c r="O68" s="9">
+        <v>10</v>
+      </c>
+      <c r="R68" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T68" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V68" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X68" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G69" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K69" s="9">
+        <v>177</v>
+      </c>
+      <c r="M69" s="3">
+        <v>20</v>
+      </c>
+      <c r="O69" s="9">
+        <v>10</v>
+      </c>
+      <c r="R69" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="T69" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V69" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X69" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K70" s="9">
+        <v>177</v>
+      </c>
+      <c r="M70" s="3">
+        <v>20</v>
+      </c>
+      <c r="O70" s="9">
+        <v>10</v>
+      </c>
+      <c r="R70" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="T70" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V70" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X70" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K71" s="9">
+        <v>177</v>
+      </c>
+      <c r="M71" s="3">
+        <v>20</v>
+      </c>
+      <c r="O71" s="9">
+        <v>10</v>
+      </c>
+      <c r="R71" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="T71" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V71" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X71" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K72" s="9">
+        <v>178</v>
+      </c>
+      <c r="M72" s="3">
+        <v>20</v>
+      </c>
+      <c r="O72" s="9">
+        <v>10</v>
+      </c>
+      <c r="R72" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="T72" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V72" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X72" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K73" s="9">
+        <v>178</v>
+      </c>
+      <c r="M73" s="3">
+        <v>21</v>
+      </c>
+      <c r="O73" s="9">
+        <v>10</v>
+      </c>
+      <c r="R73" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="T73" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V73" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X73" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I74" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K74" s="9">
+        <v>178</v>
+      </c>
+      <c r="M74" s="3">
+        <v>21</v>
+      </c>
+      <c r="O74" s="9">
+        <v>10</v>
+      </c>
+      <c r="R74" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="T74" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="V74" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="X74" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K75" s="9">
+        <v>180</v>
+      </c>
+      <c r="M75" s="3">
+        <v>21</v>
+      </c>
+      <c r="O75" s="9">
+        <v>10</v>
+      </c>
+      <c r="R75" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="T75" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="V75" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X75" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I76" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K76" s="9">
+        <v>180</v>
+      </c>
+      <c r="M76" s="3">
+        <v>21</v>
+      </c>
+      <c r="O76" s="9">
+        <v>10</v>
+      </c>
+      <c r="R76" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T76" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="V76" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X76" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K77" s="9">
+        <v>182</v>
+      </c>
+      <c r="M77" s="3">
+        <v>21</v>
+      </c>
+      <c r="O77" s="9">
+        <v>10</v>
+      </c>
+      <c r="R77" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T77" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="V77" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X77" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K78" s="9">
+        <v>182</v>
+      </c>
+      <c r="M78" s="3">
+        <v>21</v>
+      </c>
+      <c r="O78" s="9">
+        <v>10</v>
+      </c>
+      <c r="R78" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T78" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="V78" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X78" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K79" s="9">
+        <v>182</v>
+      </c>
+      <c r="M79" s="3">
+        <v>21</v>
+      </c>
+      <c r="O79" s="9">
+        <v>11</v>
+      </c>
+      <c r="R79" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T79" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="V79" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X79" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K80" s="9">
+        <v>183</v>
+      </c>
+      <c r="M80" s="3">
+        <v>21</v>
+      </c>
+      <c r="O80" s="9">
+        <v>12</v>
+      </c>
+      <c r="R80" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T80" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="V80" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X80" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G81" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K81" s="9">
+        <v>183</v>
+      </c>
+      <c r="M81" s="3">
+        <v>22</v>
+      </c>
+      <c r="O81" s="9">
+        <v>12</v>
+      </c>
+      <c r="R81" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T81" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="V81" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X81" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K82" s="9">
+        <v>183</v>
+      </c>
+      <c r="M82" s="3">
+        <v>22</v>
+      </c>
+      <c r="O82" s="9">
+        <v>12</v>
+      </c>
+      <c r="R82" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T82" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="V82" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X82" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K83" s="9">
+        <v>184</v>
+      </c>
+      <c r="M83" s="3">
+        <v>22</v>
+      </c>
+      <c r="O83" s="9">
+        <v>12</v>
+      </c>
+      <c r="R83" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T83" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="V83" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K84" s="9">
+        <v>185</v>
+      </c>
+      <c r="M84" s="3">
+        <v>22</v>
+      </c>
+      <c r="O84" s="9">
+        <v>12</v>
+      </c>
+      <c r="R84" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T84" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="V84" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X84" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K85" s="9">
+        <v>185</v>
+      </c>
+      <c r="M85" s="3">
+        <v>22</v>
+      </c>
+      <c r="O85" s="9">
+        <v>14</v>
+      </c>
+      <c r="R85" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T85" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="V85" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X85" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I86" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K86" s="9">
+        <v>186</v>
+      </c>
+      <c r="M86" s="3">
+        <v>23</v>
+      </c>
+      <c r="O86" s="9">
+        <v>15</v>
+      </c>
+      <c r="R86" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T86" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="V86" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X86" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K87" s="9">
+        <v>187</v>
+      </c>
+      <c r="M87" s="3">
+        <v>24</v>
+      </c>
+      <c r="O87" s="9">
+        <v>15</v>
+      </c>
+      <c r="R87" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T87" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="V87" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X87" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K88" s="9">
+        <v>188</v>
+      </c>
+      <c r="M88" s="3">
+        <v>24</v>
+      </c>
+      <c r="O88" s="9">
+        <v>15</v>
+      </c>
+      <c r="R88" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T88" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="V88" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X88" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K89" s="9">
+        <v>190</v>
+      </c>
+      <c r="M89" s="3">
+        <v>26</v>
+      </c>
+      <c r="O89" s="9">
+        <v>16</v>
+      </c>
+      <c r="R89" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T89" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="V89" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K90" s="9">
+        <v>190</v>
+      </c>
+      <c r="M90" s="3">
+        <v>26</v>
+      </c>
+      <c r="O90" s="9">
+        <v>18</v>
+      </c>
+      <c r="R90" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T90" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="V90" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X90" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="C91" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G91" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K91" s="9">
+        <v>194</v>
+      </c>
+      <c r="M91" s="3">
+        <v>30</v>
+      </c>
+      <c r="O91" s="9">
+        <v>20</v>
+      </c>
+      <c r="R91" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T91" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="V91" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="X91" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="C92" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G92" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I92" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K92" s="10">
+        <v>195</v>
+      </c>
+      <c r="M92" s="4">
+        <v>38</v>
+      </c>
+      <c r="O92" s="10">
+        <v>20</v>
+      </c>
+      <c r="R92" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="T92" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="V92" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="X92" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="X2:X102">
+    <sortCondition ref="X2:X102"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.39370078740157483" right="0.11811023622047245" top="0.39370078740157483" bottom="0.39370078740157483" header="0.11811023622047245" footer="0.11811023622047245"/>
+  <pageSetup paperSize="9" scale="63" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"-,Negrito"&amp;14Levantamento - Turmas Estatística 2026&amp;Cdados agrupados por categorias e valores (por variável)</oddHeader>
+  </headerFooter>
+</worksheet>
 </file>
--- a/data/dados-turmas-2026.xlsx
+++ b/data/dados-turmas-2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\estatinfo\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\estatinfo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDC9265-B70D-4257-B66A-22A961E5F4BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E748E079-D148-46D1-811B-6B51FA9E7660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="3" r:id="rId1"/>
@@ -221,7 +221,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -231,6 +231,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -299,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -315,6 +321,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -579,22 +588,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D60CCD58-E5F4-4C6F-A78C-39DF9E1D4064}">
   <dimension ref="A1:K92"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="34" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
@@ -629,7 +638,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -637,34 +646,34 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H2" t="s">
         <v>9</v>
       </c>
       <c r="I2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -672,69 +681,69 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E3">
+        <v>173</v>
+      </c>
+      <c r="F3">
+        <v>18</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4">
         <v>176</v>
       </c>
-      <c r="F3">
-        <v>18</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4">
-        <v>175</v>
-      </c>
       <c r="F4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H4" t="s">
         <v>9</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J4" t="s">
         <v>13</v>
       </c>
       <c r="K4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -742,19 +751,19 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H5" t="s">
         <v>9</v>
@@ -763,13 +772,13 @@
         <v>5</v>
       </c>
       <c r="J5" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -777,19 +786,19 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E6">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="F6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H6" t="s">
         <v>9</v>
@@ -798,33 +807,33 @@
         <v>5</v>
       </c>
       <c r="J6" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="K6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F7">
         <v>19</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H7" t="s">
         <v>9</v>
@@ -833,13 +842,13 @@
         <v>5</v>
       </c>
       <c r="J7" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -847,69 +856,69 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D8" t="s">
         <v>3</v>
       </c>
       <c r="E8">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F8">
         <v>19</v>
       </c>
       <c r="G8">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J8" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E9">
         <v>173</v>
       </c>
       <c r="F9">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G9">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I9" t="s">
         <v>5</v>
       </c>
       <c r="J9" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -917,19 +926,19 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E10">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H10" t="s">
         <v>9</v>
@@ -938,33 +947,33 @@
         <v>5</v>
       </c>
       <c r="J10" t="s">
+        <v>6</v>
+      </c>
+      <c r="K10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11">
+        <v>170</v>
+      </c>
+      <c r="F11">
         <v>20</v>
       </c>
-      <c r="K10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11">
-        <v>163</v>
-      </c>
-      <c r="F11">
-        <v>18</v>
-      </c>
       <c r="G11">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H11" t="s">
         <v>9</v>
@@ -973,68 +982,68 @@
         <v>5</v>
       </c>
       <c r="J11" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K11" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E12">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F12">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I12" t="s">
         <v>5</v>
       </c>
       <c r="J12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E13">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="F13">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G13">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H13" t="s">
         <v>9</v>
@@ -1043,33 +1052,33 @@
         <v>5</v>
       </c>
       <c r="J13" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D14" t="s">
         <v>23</v>
       </c>
       <c r="E14">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="F14">
         <v>18</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H14" t="s">
         <v>9</v>
@@ -1078,33 +1087,33 @@
         <v>5</v>
       </c>
       <c r="J14" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E15">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="F15">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G15">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H15" t="s">
         <v>9</v>
@@ -1113,30 +1122,30 @@
         <v>5</v>
       </c>
       <c r="J15" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="K15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E16">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="F16">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G16">
         <v>3</v>
@@ -1148,68 +1157,68 @@
         <v>5</v>
       </c>
       <c r="J16" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17">
+        <v>167</v>
+      </c>
+      <c r="F17">
+        <v>19</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+      <c r="H17" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" t="s">
+        <v>21</v>
+      </c>
+      <c r="K17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17">
-        <v>195</v>
-      </c>
-      <c r="F17">
-        <v>19</v>
-      </c>
-      <c r="G17">
-        <v>7</v>
-      </c>
-      <c r="H17" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" t="s">
-        <v>5</v>
-      </c>
-      <c r="J17" t="s">
-        <v>13</v>
-      </c>
-      <c r="K17" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C18" t="s">
         <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E18">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="F18">
         <v>19</v>
       </c>
       <c r="G18">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H18" t="s">
         <v>9</v>
@@ -1218,13 +1227,13 @@
         <v>5</v>
       </c>
       <c r="J18" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -1232,104 +1241,104 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E19">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="F19">
         <v>19</v>
       </c>
       <c r="G19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H19" t="s">
         <v>9</v>
       </c>
       <c r="I19" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J19" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E20">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="F20">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G20">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I20" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J20" t="s">
         <v>6</v>
       </c>
       <c r="K20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D21" t="s">
         <v>23</v>
       </c>
       <c r="E21">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="F21">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G21">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H21" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I21" t="s">
         <v>5</v>
       </c>
       <c r="J21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>0</v>
       </c>
@@ -1337,34 +1346,34 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22">
+        <v>183</v>
+      </c>
+      <c r="F22">
+        <v>21</v>
+      </c>
+      <c r="G22">
         <v>3</v>
-      </c>
-      <c r="E22">
-        <v>170</v>
-      </c>
-      <c r="F22">
-        <v>20</v>
-      </c>
-      <c r="G22">
-        <v>10</v>
       </c>
       <c r="H22" t="s">
         <v>9</v>
       </c>
       <c r="I22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J22" t="s">
         <v>21</v>
       </c>
       <c r="K22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>0</v>
       </c>
@@ -1372,19 +1381,19 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E23">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F23">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" t="s">
         <v>9</v>
@@ -1393,68 +1402,68 @@
         <v>5</v>
       </c>
       <c r="J23" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24">
+        <v>164</v>
+      </c>
+      <c r="F24">
         <v>23</v>
       </c>
-      <c r="E24">
-        <v>173</v>
-      </c>
-      <c r="F24">
-        <v>19</v>
-      </c>
       <c r="G24">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H24" t="s">
         <v>9</v>
       </c>
       <c r="I24" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J24" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="K24" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D25" t="s">
         <v>23</v>
       </c>
       <c r="E25">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="F25">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H25" t="s">
         <v>9</v>
@@ -1463,39 +1472,39 @@
         <v>5</v>
       </c>
       <c r="J25" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E26">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F26">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G26">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H26" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I26" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J26" t="s">
         <v>20</v>
@@ -1504,30 +1513,30 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D27" t="s">
         <v>3</v>
       </c>
       <c r="E27">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F27">
         <v>18</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I27" t="s">
         <v>5</v>
@@ -1536,10 +1545,10 @@
         <v>6</v>
       </c>
       <c r="K27" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>0</v>
       </c>
@@ -1547,54 +1556,54 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E28">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F28">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="I28" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J28" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K28" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
         <v>18</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D29" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E29">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="F29">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G29">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H29" t="s">
         <v>9</v>
@@ -1603,13 +1612,13 @@
         <v>5</v>
       </c>
       <c r="J29" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="K29" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>0</v>
       </c>
@@ -1617,34 +1626,34 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E30">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F30">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G30">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H30" t="s">
         <v>9</v>
       </c>
       <c r="I30" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J30" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K30" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>0</v>
       </c>
@@ -1652,19 +1661,19 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E31">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F31">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G31">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H31" t="s">
         <v>9</v>
@@ -1676,68 +1685,68 @@
         <v>20</v>
       </c>
       <c r="K31" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D32" t="s">
         <v>19</v>
       </c>
       <c r="E32">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="F32">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G32">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H32" t="s">
         <v>9</v>
       </c>
       <c r="I32" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J32" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K32" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33">
+        <v>173</v>
+      </c>
+      <c r="F33">
         <v>24</v>
-      </c>
-      <c r="E33">
-        <v>187</v>
-      </c>
-      <c r="F33">
-        <v>20</v>
       </c>
       <c r="G33">
         <v>4</v>
       </c>
       <c r="H33" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I33" t="s">
         <v>5</v>
@@ -1749,7 +1758,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>0</v>
       </c>
@@ -1757,19 +1766,19 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E34">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F34">
         <v>18</v>
       </c>
       <c r="G34">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H34" t="s">
         <v>9</v>
@@ -1781,24 +1790,24 @@
         <v>13</v>
       </c>
       <c r="K34" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C35" t="s">
         <v>2</v>
       </c>
       <c r="D35" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E35">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="F35">
         <v>19</v>
@@ -1810,51 +1819,51 @@
         <v>9</v>
       </c>
       <c r="I35" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J35" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>27</v>
+      </c>
+      <c r="B36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" t="s">
+        <v>3</v>
+      </c>
+      <c r="E36">
+        <v>165</v>
+      </c>
+      <c r="F36">
+        <v>19</v>
+      </c>
+      <c r="G36">
+        <v>5</v>
+      </c>
+      <c r="H36" t="s">
+        <v>4</v>
+      </c>
+      <c r="I36" t="s">
+        <v>5</v>
+      </c>
+      <c r="J36" t="s">
+        <v>13</v>
+      </c>
+      <c r="K36" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B36" t="s">
-        <v>1</v>
-      </c>
-      <c r="C36" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" t="s">
-        <v>23</v>
-      </c>
-      <c r="E36">
-        <v>171</v>
-      </c>
-      <c r="F36">
-        <v>19</v>
-      </c>
-      <c r="G36">
-        <v>8</v>
-      </c>
-      <c r="H36" t="s">
-        <v>9</v>
-      </c>
-      <c r="I36" t="s">
-        <v>5</v>
-      </c>
-      <c r="J36" t="s">
-        <v>21</v>
-      </c>
-      <c r="K36" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>0</v>
       </c>
@@ -1862,34 +1871,34 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E37">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="F37">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H37" t="s">
         <v>9</v>
       </c>
       <c r="I37" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J37" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K37" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>0</v>
       </c>
@@ -1903,13 +1912,13 @@
         <v>23</v>
       </c>
       <c r="E38">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="F38">
         <v>19</v>
       </c>
       <c r="G38">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H38" t="s">
         <v>9</v>
@@ -1921,10 +1930,10 @@
         <v>13</v>
       </c>
       <c r="K38" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>0</v>
       </c>
@@ -1935,33 +1944,33 @@
         <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E39">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="F39">
         <v>19</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H39" t="s">
         <v>9</v>
       </c>
       <c r="I39" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J39" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="K39" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B40" t="s">
         <v>1</v>
@@ -1970,36 +1979,36 @@
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E40">
         <v>175</v>
       </c>
       <c r="F40">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G40">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H40" t="s">
         <v>9</v>
       </c>
       <c r="I40" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J40" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K40" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C41" t="s">
         <v>2</v>
@@ -2008,51 +2017,51 @@
         <v>23</v>
       </c>
       <c r="E41">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="F41">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G41">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H41" t="s">
+        <v>9</v>
+      </c>
+      <c r="I41" t="s">
+        <v>5</v>
+      </c>
+      <c r="J41" t="s">
+        <v>13</v>
+      </c>
+      <c r="K41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42">
+        <v>188</v>
+      </c>
+      <c r="F42">
         <v>22</v>
       </c>
-      <c r="I41" t="s">
-        <v>5</v>
-      </c>
-      <c r="J41" t="s">
-        <v>6</v>
-      </c>
-      <c r="K41" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>0</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1</v>
-      </c>
-      <c r="C42" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" t="s">
-        <v>23</v>
-      </c>
-      <c r="E42">
-        <v>185</v>
-      </c>
-      <c r="F42">
-        <v>19</v>
-      </c>
       <c r="G42">
         <v>5</v>
       </c>
       <c r="H42" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I42" t="s">
         <v>5</v>
@@ -2061,12 +2070,12 @@
         <v>13</v>
       </c>
       <c r="K42" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B43" t="s">
         <v>1</v>
@@ -2075,19 +2084,19 @@
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E43">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F43">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G43">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H43" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I43" t="s">
         <v>5</v>
@@ -2096,10 +2105,10 @@
         <v>13</v>
       </c>
       <c r="K43" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>0</v>
       </c>
@@ -2107,51 +2116,51 @@
         <v>18</v>
       </c>
       <c r="C44" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E44">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F44">
         <v>18</v>
       </c>
       <c r="G44">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H44" t="s">
         <v>9</v>
       </c>
       <c r="I44" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J44" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K44" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B45" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C45" t="s">
         <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E45">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="F45">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G45">
         <v>6</v>
@@ -2163,48 +2172,48 @@
         <v>10</v>
       </c>
       <c r="J45" t="s">
+        <v>21</v>
+      </c>
+      <c r="K45" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46">
+        <v>159</v>
+      </c>
+      <c r="F46">
+        <v>19</v>
+      </c>
+      <c r="G46">
         <v>6</v>
-      </c>
-      <c r="K45" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B46" t="s">
-        <v>1</v>
-      </c>
-      <c r="C46" t="s">
-        <v>2</v>
-      </c>
-      <c r="D46" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46">
-        <v>176</v>
-      </c>
-      <c r="F46">
-        <v>19</v>
-      </c>
-      <c r="G46">
-        <v>8</v>
       </c>
       <c r="H46" t="s">
         <v>9</v>
       </c>
       <c r="I46" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J46" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K46" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>0</v>
       </c>
@@ -2215,7 +2224,7 @@
         <v>8</v>
       </c>
       <c r="D47" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E47">
         <v>160</v>
@@ -2224,7 +2233,7 @@
         <v>19</v>
       </c>
       <c r="G47">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H47" t="s">
         <v>9</v>
@@ -2233,13 +2242,13 @@
         <v>5</v>
       </c>
       <c r="J47" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K47" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>0</v>
       </c>
@@ -2247,139 +2256,139 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D48" t="s">
         <v>23</v>
       </c>
       <c r="E48">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F48">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H48" t="s">
         <v>9</v>
       </c>
       <c r="I48" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J48" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="K48" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49">
+        <v>176</v>
+      </c>
+      <c r="F49">
+        <v>19</v>
+      </c>
+      <c r="G49">
+        <v>6</v>
+      </c>
+      <c r="H49" t="s">
+        <v>9</v>
+      </c>
+      <c r="I49" t="s">
+        <v>5</v>
+      </c>
+      <c r="J49" t="s">
+        <v>13</v>
+      </c>
+      <c r="K49" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>0</v>
-      </c>
-      <c r="B49" t="s">
-        <v>18</v>
-      </c>
-      <c r="C49" t="s">
-        <v>2</v>
-      </c>
-      <c r="D49" t="s">
-        <v>3</v>
-      </c>
-      <c r="E49">
-        <v>164</v>
-      </c>
-      <c r="F49">
-        <v>19</v>
-      </c>
-      <c r="G49">
-        <v>2</v>
-      </c>
-      <c r="H49" t="s">
-        <v>22</v>
-      </c>
-      <c r="I49" t="s">
-        <v>10</v>
-      </c>
-      <c r="J49" t="s">
-        <v>6</v>
-      </c>
-      <c r="K49" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B50" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D50" t="s">
         <v>23</v>
       </c>
       <c r="E50">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="F50">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G50">
         <v>6</v>
       </c>
       <c r="H50" t="s">
+        <v>4</v>
+      </c>
+      <c r="I50" t="s">
+        <v>5</v>
+      </c>
+      <c r="J50" t="s">
+        <v>13</v>
+      </c>
+      <c r="K50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51">
+        <v>197</v>
+      </c>
+      <c r="F51">
+        <v>20</v>
+      </c>
+      <c r="G51">
+        <v>6</v>
+      </c>
+      <c r="H51" t="s">
         <v>9</v>
       </c>
-      <c r="I50" t="s">
-        <v>5</v>
-      </c>
-      <c r="J50" t="s">
+      <c r="I51" t="s">
+        <v>5</v>
+      </c>
+      <c r="J51" t="s">
         <v>6</v>
       </c>
-      <c r="K50" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>0</v>
-      </c>
-      <c r="B51" t="s">
-        <v>1</v>
-      </c>
-      <c r="C51" t="s">
-        <v>2</v>
-      </c>
-      <c r="D51" t="s">
-        <v>24</v>
-      </c>
-      <c r="E51">
-        <v>182</v>
-      </c>
-      <c r="F51">
-        <v>18</v>
-      </c>
-      <c r="G51">
-        <v>18</v>
-      </c>
-      <c r="H51" t="s">
-        <v>26</v>
-      </c>
-      <c r="I51" t="s">
-        <v>10</v>
-      </c>
-      <c r="J51" t="s">
-        <v>13</v>
-      </c>
       <c r="K51" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>0</v>
       </c>
@@ -2387,60 +2396,60 @@
         <v>18</v>
       </c>
       <c r="C52" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D52" t="s">
         <v>19</v>
       </c>
       <c r="E52">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F52">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G52">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H52" t="s">
         <v>9</v>
       </c>
       <c r="I52" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J52" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K52" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C53" t="s">
         <v>2</v>
       </c>
       <c r="D53" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E53">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F53">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H53" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I53" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J53" t="s">
         <v>20</v>
@@ -2449,42 +2458,42 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B54" t="s">
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D54" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E54">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="F54">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H54" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I54" t="s">
         <v>5</v>
       </c>
       <c r="J54" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K54" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>0</v>
       </c>
@@ -2495,19 +2504,19 @@
         <v>2</v>
       </c>
       <c r="D55" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E55">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="F55">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H55" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I55" t="s">
         <v>5</v>
@@ -2516,10 +2525,10 @@
         <v>13</v>
       </c>
       <c r="K55" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>0</v>
       </c>
@@ -2554,27 +2563,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>0</v>
       </c>
       <c r="B57" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C57" t="s">
         <v>12</v>
       </c>
       <c r="D57" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E57">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="F57">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G57">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H57" t="s">
         <v>9</v>
@@ -2583,13 +2592,13 @@
         <v>5</v>
       </c>
       <c r="J57" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K57" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>0</v>
       </c>
@@ -2600,16 +2609,16 @@
         <v>15</v>
       </c>
       <c r="D58" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E58">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F58">
         <v>19</v>
       </c>
       <c r="G58">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H58" t="s">
         <v>9</v>
@@ -2621,10 +2630,10 @@
         <v>21</v>
       </c>
       <c r="K58" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>0</v>
       </c>
@@ -2635,16 +2644,16 @@
         <v>2</v>
       </c>
       <c r="D59" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E59">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F59">
         <v>19</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H59" t="s">
         <v>9</v>
@@ -2659,9 +2668,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B60" t="s">
         <v>1</v>
@@ -2682,19 +2691,19 @@
         <v>8</v>
       </c>
       <c r="H60" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I60" t="s">
         <v>5</v>
       </c>
       <c r="J60" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K60" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>0</v>
       </c>
@@ -2708,13 +2717,13 @@
         <v>24</v>
       </c>
       <c r="E61">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F61">
         <v>19</v>
       </c>
       <c r="G61">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H61" t="s">
         <v>9</v>
@@ -2726,45 +2735,45 @@
         <v>13</v>
       </c>
       <c r="K61" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B62" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C62" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D62" t="s">
         <v>24</v>
       </c>
       <c r="E62">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="F62">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G62">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H62" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I62" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J62" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K62" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>0</v>
       </c>
@@ -2772,69 +2781,69 @@
         <v>1</v>
       </c>
       <c r="C63" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D63" t="s">
         <v>3</v>
       </c>
       <c r="E63">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="F63">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G63">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H63" t="s">
         <v>9</v>
       </c>
       <c r="I63" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J63" t="s">
         <v>6</v>
       </c>
       <c r="K63" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C64" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D64" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E64">
         <v>170</v>
       </c>
       <c r="F64">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H64" t="s">
         <v>9</v>
       </c>
       <c r="I64" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J64" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K64" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>0</v>
       </c>
@@ -2851,10 +2860,10 @@
         <v>176</v>
       </c>
       <c r="F65">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G65">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H65" t="s">
         <v>9</v>
@@ -2863,13 +2872,13 @@
         <v>5</v>
       </c>
       <c r="J65" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K65" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>0</v>
       </c>
@@ -2877,60 +2886,60 @@
         <v>1</v>
       </c>
       <c r="C66" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D66" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E66">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F66">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G66">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H66" t="s">
         <v>9</v>
       </c>
       <c r="I66" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J66" t="s">
         <v>6</v>
       </c>
       <c r="K66" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B67" t="s">
         <v>18</v>
       </c>
       <c r="C67" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D67" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E67">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F67">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G67">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H67" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I67" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J67" t="s">
         <v>13</v>
@@ -2939,147 +2948,147 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B68" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C68" t="s">
         <v>15</v>
       </c>
       <c r="D68" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E68">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="F68">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H68" t="s">
         <v>9</v>
       </c>
       <c r="I68" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J68" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K68" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B69" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C69" t="s">
         <v>15</v>
       </c>
       <c r="D69" t="s">
+        <v>19</v>
+      </c>
+      <c r="E69">
+        <v>157</v>
+      </c>
+      <c r="F69">
+        <v>19</v>
+      </c>
+      <c r="G69">
+        <v>10</v>
+      </c>
+      <c r="H69" t="s">
+        <v>9</v>
+      </c>
+      <c r="I69" t="s">
+        <v>5</v>
+      </c>
+      <c r="J69" t="s">
+        <v>21</v>
+      </c>
+      <c r="K69" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B70" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" t="s">
+        <v>2</v>
+      </c>
+      <c r="D70" t="s">
         <v>23</v>
       </c>
-      <c r="E69">
-        <v>173</v>
-      </c>
-      <c r="F69">
-        <v>24</v>
-      </c>
-      <c r="G69">
-        <v>4</v>
-      </c>
-      <c r="H69" t="s">
-        <v>4</v>
-      </c>
-      <c r="I69" t="s">
-        <v>5</v>
-      </c>
-      <c r="J69" t="s">
+      <c r="E70">
+        <v>158</v>
+      </c>
+      <c r="F70">
+        <v>19</v>
+      </c>
+      <c r="G70">
+        <v>10</v>
+      </c>
+      <c r="H70" t="s">
+        <v>9</v>
+      </c>
+      <c r="I70" t="s">
+        <v>5</v>
+      </c>
+      <c r="J70" t="s">
         <v>13</v>
-      </c>
-      <c r="K69" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>27</v>
-      </c>
-      <c r="B70" t="s">
-        <v>18</v>
-      </c>
-      <c r="C70" t="s">
-        <v>2</v>
-      </c>
-      <c r="D70" t="s">
-        <v>24</v>
-      </c>
-      <c r="E70">
-        <v>155</v>
-      </c>
-      <c r="F70">
-        <v>21</v>
-      </c>
-      <c r="G70">
-        <v>8</v>
-      </c>
-      <c r="H70" t="s">
-        <v>4</v>
-      </c>
-      <c r="I70" t="s">
-        <v>10</v>
-      </c>
-      <c r="J70" t="s">
-        <v>21</v>
       </c>
       <c r="K70" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B71" t="s">
         <v>18</v>
       </c>
       <c r="C71" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D71" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E71">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="F71">
         <v>19</v>
       </c>
       <c r="G71">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H71" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I71" t="s">
         <v>5</v>
       </c>
       <c r="J71" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K71" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>27</v>
       </c>
@@ -3087,48 +3096,48 @@
         <v>18</v>
       </c>
       <c r="C72" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D72" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E72">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F72">
         <v>19</v>
       </c>
       <c r="G72">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H72" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I72" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J72" t="s">
         <v>21</v>
       </c>
       <c r="K72" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B73" t="s">
         <v>18</v>
       </c>
       <c r="C73" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D73" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E73">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="F73">
         <v>19</v>
@@ -3137,77 +3146,77 @@
         <v>10</v>
       </c>
       <c r="H73" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I73" t="s">
         <v>5</v>
       </c>
       <c r="J73" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K73" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B74" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C74" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D74" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E74">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F74">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G74">
+        <v>10</v>
+      </c>
+      <c r="H74" t="s">
+        <v>22</v>
+      </c>
+      <c r="I74" t="s">
+        <v>5</v>
+      </c>
+      <c r="J74" t="s">
         <v>6</v>
       </c>
-      <c r="H74" t="s">
-        <v>9</v>
-      </c>
-      <c r="I74" t="s">
-        <v>10</v>
-      </c>
-      <c r="J74" t="s">
-        <v>21</v>
-      </c>
       <c r="K74" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>27</v>
       </c>
       <c r="B75" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C75" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D75" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E75">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="F75">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G75">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H75" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I75" t="s">
         <v>5</v>
@@ -3216,10 +3225,10 @@
         <v>13</v>
       </c>
       <c r="K75" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>27</v>
       </c>
@@ -3233,65 +3242,65 @@
         <v>23</v>
       </c>
       <c r="E76">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="F76">
         <v>19</v>
       </c>
       <c r="G76">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H76" t="s">
+        <v>4</v>
+      </c>
+      <c r="I76" t="s">
+        <v>5</v>
+      </c>
+      <c r="J76" t="s">
+        <v>20</v>
+      </c>
+      <c r="K76" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>0</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1</v>
+      </c>
+      <c r="C77" t="s">
+        <v>2</v>
+      </c>
+      <c r="D77" t="s">
+        <v>3</v>
+      </c>
+      <c r="E77">
+        <v>170</v>
+      </c>
+      <c r="F77">
+        <v>20</v>
+      </c>
+      <c r="G77">
+        <v>10</v>
+      </c>
+      <c r="H77" t="s">
         <v>9</v>
       </c>
-      <c r="I76" t="s">
-        <v>5</v>
-      </c>
-      <c r="J76" t="s">
-        <v>13</v>
-      </c>
-      <c r="K76" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>27</v>
-      </c>
-      <c r="B77" t="s">
-        <v>18</v>
-      </c>
-      <c r="C77" t="s">
-        <v>2</v>
-      </c>
-      <c r="D77" t="s">
-        <v>19</v>
-      </c>
-      <c r="E77">
-        <v>176</v>
-      </c>
-      <c r="F77">
+      <c r="I77" t="s">
+        <v>10</v>
+      </c>
+      <c r="J77" t="s">
         <v>21</v>
       </c>
-      <c r="G77">
-        <v>6</v>
-      </c>
-      <c r="H77" t="s">
-        <v>4</v>
-      </c>
-      <c r="I77" t="s">
-        <v>5</v>
-      </c>
-      <c r="J77" t="s">
-        <v>20</v>
-      </c>
       <c r="K77" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B78" t="s">
         <v>1</v>
@@ -3300,19 +3309,19 @@
         <v>2</v>
       </c>
       <c r="D78" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E78">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F78">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G78">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H78" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I78" t="s">
         <v>5</v>
@@ -3321,30 +3330,30 @@
         <v>21</v>
       </c>
       <c r="K78" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B79" t="s">
         <v>1</v>
       </c>
       <c r="C79" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D79" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E79">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="F79">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G79">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H79" t="s">
         <v>9</v>
@@ -3356,36 +3365,36 @@
         <v>13</v>
       </c>
       <c r="K79" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B80" t="s">
         <v>1</v>
       </c>
       <c r="C80" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" t="s">
+        <v>16</v>
+      </c>
+      <c r="E80">
+        <v>190</v>
+      </c>
+      <c r="F80">
+        <v>18</v>
+      </c>
+      <c r="G80">
         <v>12</v>
       </c>
-      <c r="D80" t="s">
-        <v>3</v>
-      </c>
-      <c r="E80">
-        <v>176</v>
-      </c>
-      <c r="F80">
-        <v>38</v>
-      </c>
-      <c r="G80">
-        <v>2</v>
-      </c>
       <c r="H80" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I80" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J80" t="s">
         <v>20</v>
@@ -3394,42 +3403,42 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C81" t="s">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D81" t="s">
         <v>23</v>
       </c>
       <c r="E81">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F81">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G81">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H81" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I81" t="s">
         <v>5</v>
       </c>
       <c r="J81" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K81" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>27</v>
       </c>
@@ -3437,54 +3446,54 @@
         <v>18</v>
       </c>
       <c r="C82" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D82" t="s">
         <v>23</v>
       </c>
       <c r="E82">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="F82">
         <v>19</v>
       </c>
       <c r="G82">
+        <v>12</v>
+      </c>
+      <c r="H82" t="s">
+        <v>9</v>
+      </c>
+      <c r="I82" t="s">
         <v>10</v>
       </c>
-      <c r="H82" t="s">
-        <v>4</v>
-      </c>
-      <c r="I82" t="s">
-        <v>5</v>
-      </c>
       <c r="J82" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K82" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B83" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C83" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D83" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E83">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F83">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G83">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H83" t="s">
         <v>9</v>
@@ -3496,15 +3505,15 @@
         <v>6</v>
       </c>
       <c r="K83" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C84" t="s">
         <v>2</v>
@@ -3513,13 +3522,13 @@
         <v>23</v>
       </c>
       <c r="E84">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F84">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G84">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H84" t="s">
         <v>4</v>
@@ -3528,33 +3537,33 @@
         <v>5</v>
       </c>
       <c r="J84" t="s">
+        <v>13</v>
+      </c>
+      <c r="K84" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>0</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1</v>
+      </c>
+      <c r="C85" t="s">
+        <v>2</v>
+      </c>
+      <c r="D85" t="s">
+        <v>19</v>
+      </c>
+      <c r="E85">
+        <v>177</v>
+      </c>
+      <c r="F85">
         <v>21</v>
       </c>
-      <c r="K84" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>27</v>
-      </c>
-      <c r="B85" t="s">
-        <v>1</v>
-      </c>
-      <c r="C85" t="s">
-        <v>2</v>
-      </c>
-      <c r="D85" t="s">
-        <v>24</v>
-      </c>
-      <c r="E85">
-        <v>178</v>
-      </c>
-      <c r="F85">
-        <v>26</v>
-      </c>
       <c r="G85">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H85" t="s">
         <v>9</v>
@@ -3563,15 +3572,15 @@
         <v>5</v>
       </c>
       <c r="J85" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K85" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B86" t="s">
         <v>18</v>
@@ -3580,33 +3589,33 @@
         <v>2</v>
       </c>
       <c r="D86" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E86">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="F86">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G86">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H86" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I86" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J86" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K86" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B87" t="s">
         <v>18</v>
@@ -3615,31 +3624,31 @@
         <v>8</v>
       </c>
       <c r="D87" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E87">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="F87">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G87">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H87" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I87" t="s">
         <v>5</v>
       </c>
       <c r="J87" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K87" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>27</v>
       </c>
@@ -3647,22 +3656,22 @@
         <v>1</v>
       </c>
       <c r="C88" t="s">
+        <v>2</v>
+      </c>
+      <c r="D88" t="s">
+        <v>24</v>
+      </c>
+      <c r="E88">
+        <v>178</v>
+      </c>
+      <c r="F88">
+        <v>26</v>
+      </c>
+      <c r="G88">
         <v>15</v>
       </c>
-      <c r="D88" t="s">
-        <v>23</v>
-      </c>
-      <c r="E88">
-        <v>190</v>
-      </c>
-      <c r="F88">
-        <v>19</v>
-      </c>
-      <c r="G88">
-        <v>3</v>
-      </c>
       <c r="H88" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="I88" t="s">
         <v>5</v>
@@ -3671,33 +3680,33 @@
         <v>21</v>
       </c>
       <c r="K88" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>27</v>
       </c>
       <c r="B89" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C89" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D89" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E89">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="F89">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G89">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="H89" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I89" t="s">
         <v>5</v>
@@ -3709,100 +3718,100 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B90" t="s">
         <v>1</v>
       </c>
       <c r="C90" t="s">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D90" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E90">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="F90">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G90">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H90" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="I90" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J90" t="s">
         <v>13</v>
       </c>
       <c r="K90" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B91" t="s">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C91" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D91" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E91">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="F91">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G91">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H91" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I91" t="s">
         <v>5</v>
       </c>
       <c r="J91" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="K91" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>27</v>
       </c>
       <c r="B92" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C92" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D92" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E92">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="F92">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G92">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H92" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I92" t="s">
         <v>5</v>
@@ -3811,10 +3820,13 @@
         <v>13</v>
       </c>
       <c r="K92" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K92">
+    <sortCondition ref="G2:G92"/>
+  </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -3822,33 +3834,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67291CED-4854-4A07-9C00-39F7F3C0BA26}">
   <dimension ref="A1:X92"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="1.88671875" customWidth="1"/>
-    <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="1.85546875" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="6" max="6" width="3" customWidth="1"/>
-    <col min="7" max="7" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="3" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="3" customWidth="1"/>
     <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="3" customWidth="1"/>
-    <col min="13" max="13" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="3" customWidth="1"/>
-    <col min="15" max="15" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="3" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="3" customWidth="1"/>
-    <col min="20" max="20" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="3" customWidth="1"/>
-    <col min="22" max="22" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.44140625" customWidth="1"/>
-    <col min="24" max="24" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.42578125" customWidth="1"/>
+    <col min="24" max="24" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C1" s="12" t="s">
         <v>28</v>
       </c>
@@ -3883,7 +3895,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3899,7 +3911,7 @@
       <c r="I2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="15">
         <v>155</v>
       </c>
       <c r="M2" s="2">
@@ -3921,7 +3933,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3937,7 +3949,7 @@
       <c r="I3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3" s="16">
         <v>155</v>
       </c>
       <c r="M3" s="3">
@@ -3959,7 +3971,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3975,7 +3987,7 @@
       <c r="I4" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="16">
         <v>155</v>
       </c>
       <c r="M4" s="3">
@@ -3997,7 +4009,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4013,7 +4025,7 @@
       <c r="I5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="16">
         <v>157</v>
       </c>
       <c r="M5" s="3">
@@ -4035,7 +4047,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4051,7 +4063,7 @@
       <c r="I6" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="16">
         <v>158</v>
       </c>
       <c r="M6" s="3">
@@ -4073,7 +4085,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4089,7 +4101,7 @@
       <c r="I7" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="16">
         <v>159</v>
       </c>
       <c r="M7" s="3">
@@ -4111,7 +4123,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4127,7 +4139,7 @@
       <c r="I8" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="16">
         <v>160</v>
       </c>
       <c r="M8" s="3">
@@ -4149,7 +4161,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4165,7 +4177,7 @@
       <c r="I9" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="16">
         <v>160</v>
       </c>
       <c r="M9" s="3">
@@ -4187,7 +4199,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4203,7 +4215,7 @@
       <c r="I10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="16">
         <v>160</v>
       </c>
       <c r="M10" s="3">
@@ -4225,7 +4237,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4241,7 +4253,7 @@
       <c r="I11" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="16">
         <v>160</v>
       </c>
       <c r="M11" s="3">
@@ -4263,7 +4275,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4279,7 +4291,7 @@
       <c r="I12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="16">
         <v>160</v>
       </c>
       <c r="M12" s="3">
@@ -4301,7 +4313,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4317,7 +4329,7 @@
       <c r="I13" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="16">
         <v>161</v>
       </c>
       <c r="M13" s="3">
@@ -4339,7 +4351,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4355,7 +4367,7 @@
       <c r="I14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="16">
         <v>161</v>
       </c>
       <c r="M14" s="3">
@@ -4377,7 +4389,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4393,7 +4405,7 @@
       <c r="I15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="16">
         <v>162</v>
       </c>
       <c r="M15" s="3">
@@ -4415,7 +4427,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4431,7 +4443,7 @@
       <c r="I16" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="16">
         <v>162</v>
       </c>
       <c r="M16" s="3">
@@ -4453,7 +4465,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4469,7 +4481,7 @@
       <c r="I17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="16">
         <v>163</v>
       </c>
       <c r="M17" s="3">
@@ -4491,7 +4503,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4507,7 +4519,7 @@
       <c r="I18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="16">
         <v>163</v>
       </c>
       <c r="M18" s="3">
@@ -4529,7 +4541,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4545,7 +4557,7 @@
       <c r="I19" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K19" s="16">
         <v>163</v>
       </c>
       <c r="M19" s="3">
@@ -4567,7 +4579,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4583,7 +4595,7 @@
       <c r="I20" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="16">
         <v>164</v>
       </c>
       <c r="M20" s="3">
@@ -4605,7 +4617,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4621,7 +4633,7 @@
       <c r="I21" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="16">
         <v>164</v>
       </c>
       <c r="M21" s="3">
@@ -4643,7 +4655,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4659,7 +4671,7 @@
       <c r="I22" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K22" s="9">
+      <c r="K22" s="16">
         <v>164</v>
       </c>
       <c r="M22" s="3">
@@ -4681,7 +4693,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4697,7 +4709,7 @@
       <c r="I23" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K23" s="9">
+      <c r="K23" s="16">
         <v>164</v>
       </c>
       <c r="M23" s="3">
@@ -4719,7 +4731,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4735,7 +4747,7 @@
       <c r="I24" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="16">
         <v>165</v>
       </c>
       <c r="M24" s="3">
@@ -4757,7 +4769,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4773,7 +4785,7 @@
       <c r="I25" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K25" s="9">
+      <c r="K25" s="16">
         <v>165</v>
       </c>
       <c r="M25" s="3">
@@ -4795,7 +4807,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4811,7 +4823,7 @@
       <c r="I26" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="16">
         <v>165</v>
       </c>
       <c r="M26" s="3">
@@ -4833,7 +4845,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4849,7 +4861,7 @@
       <c r="I27" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K27" s="9">
+      <c r="K27" s="16">
         <v>165</v>
       </c>
       <c r="M27" s="3">
@@ -4871,7 +4883,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4887,7 +4899,7 @@
       <c r="I28" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K28" s="9">
+      <c r="K28" s="16">
         <v>167</v>
       </c>
       <c r="M28" s="3">
@@ -4909,7 +4921,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4925,7 +4937,7 @@
       <c r="I29" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K29" s="9">
+      <c r="K29" s="16">
         <v>167</v>
       </c>
       <c r="M29" s="3">
@@ -4947,7 +4959,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4963,7 +4975,7 @@
       <c r="I30" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K30" s="9">
+      <c r="K30" s="16">
         <v>169</v>
       </c>
       <c r="M30" s="3">
@@ -4985,7 +4997,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5001,7 +5013,7 @@
       <c r="I31" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K31" s="9">
+      <c r="K31" s="16">
         <v>170</v>
       </c>
       <c r="M31" s="3">
@@ -5023,7 +5035,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5039,7 +5051,7 @@
       <c r="I32" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K32" s="9">
+      <c r="K32" s="16">
         <v>170</v>
       </c>
       <c r="M32" s="3">
@@ -5061,7 +5073,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5077,7 +5089,7 @@
       <c r="I33" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K33" s="9">
+      <c r="K33" s="16">
         <v>170</v>
       </c>
       <c r="M33" s="3">
@@ -5099,7 +5111,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5115,7 +5127,7 @@
       <c r="I34" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K34" s="9">
+      <c r="K34" s="16">
         <v>170</v>
       </c>
       <c r="M34" s="3">
@@ -5137,7 +5149,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5153,7 +5165,7 @@
       <c r="I35" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K35" s="9">
+      <c r="K35" s="16">
         <v>170</v>
       </c>
       <c r="M35" s="3">
@@ -5175,7 +5187,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5191,7 +5203,7 @@
       <c r="I36" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K36" s="9">
+      <c r="K36" s="16">
         <v>170</v>
       </c>
       <c r="M36" s="3">
@@ -5213,7 +5225,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5229,7 +5241,7 @@
       <c r="I37" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K37" s="9">
+      <c r="K37" s="16">
         <v>170</v>
       </c>
       <c r="M37" s="3">
@@ -5251,7 +5263,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5267,7 +5279,7 @@
       <c r="I38" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K38" s="9">
+      <c r="K38" s="16">
         <v>170</v>
       </c>
       <c r="M38" s="3">
@@ -5289,7 +5301,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5305,7 +5317,7 @@
       <c r="I39" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K39" s="9">
+      <c r="K39" s="16">
         <v>171</v>
       </c>
       <c r="M39" s="3">
@@ -5327,7 +5339,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5343,7 +5355,7 @@
       <c r="I40" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K40" s="9">
+      <c r="K40" s="16">
         <v>172</v>
       </c>
       <c r="M40" s="3">
@@ -5365,7 +5377,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5381,7 +5393,7 @@
       <c r="I41" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K41" s="9">
+      <c r="K41" s="16">
         <v>172</v>
       </c>
       <c r="M41" s="3">
@@ -5403,7 +5415,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5419,7 +5431,7 @@
       <c r="I42" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K42" s="9">
+      <c r="K42" s="16">
         <v>172</v>
       </c>
       <c r="M42" s="3">
@@ -5441,7 +5453,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5457,7 +5469,7 @@
       <c r="I43" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K43" s="9">
+      <c r="K43" s="16">
         <v>173</v>
       </c>
       <c r="M43" s="3">
@@ -5479,7 +5491,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5495,7 +5507,7 @@
       <c r="I44" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K44" s="9">
+      <c r="K44" s="16">
         <v>173</v>
       </c>
       <c r="M44" s="3">
@@ -5517,7 +5529,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5533,7 +5545,7 @@
       <c r="I45" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K45" s="9">
+      <c r="K45" s="16">
         <v>173</v>
       </c>
       <c r="M45" s="3">
@@ -5555,7 +5567,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5571,7 +5583,7 @@
       <c r="I46" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K46" s="9">
+      <c r="K46" s="16">
         <v>173</v>
       </c>
       <c r="M46" s="3">
@@ -5593,7 +5605,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5609,7 +5621,7 @@
       <c r="I47" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K47" s="9">
+      <c r="K47" s="16">
         <v>173</v>
       </c>
       <c r="M47" s="3">
@@ -5631,7 +5643,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5647,7 +5659,7 @@
       <c r="I48" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K48" s="9">
+      <c r="K48" s="16">
         <v>173</v>
       </c>
       <c r="M48" s="3">
@@ -5669,7 +5681,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5685,7 +5697,7 @@
       <c r="I49" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K49" s="9">
+      <c r="K49" s="16">
         <v>173</v>
       </c>
       <c r="M49" s="3">
@@ -5707,7 +5719,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5723,7 +5735,7 @@
       <c r="I50" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K50" s="9">
+      <c r="K50" s="16">
         <v>173</v>
       </c>
       <c r="M50" s="3">
@@ -5745,7 +5757,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5761,7 +5773,7 @@
       <c r="I51" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K51" s="9">
+      <c r="K51" s="16">
         <v>174</v>
       </c>
       <c r="M51" s="3">
@@ -5783,7 +5795,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5799,7 +5811,7 @@
       <c r="I52" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K52" s="9">
+      <c r="K52" s="16">
         <v>174</v>
       </c>
       <c r="M52" s="3">
@@ -5821,7 +5833,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5837,7 +5849,7 @@
       <c r="I53" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K53" s="9">
+      <c r="K53" s="16">
         <v>174</v>
       </c>
       <c r="M53" s="3">
@@ -5859,7 +5871,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5875,7 +5887,7 @@
       <c r="I54" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K54" s="9">
+      <c r="K54" s="16">
         <v>175</v>
       </c>
       <c r="M54" s="3">
@@ -5897,7 +5909,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5913,7 +5925,7 @@
       <c r="I55" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K55" s="9">
+      <c r="K55" s="16">
         <v>175</v>
       </c>
       <c r="M55" s="3">
@@ -5935,7 +5947,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5951,7 +5963,7 @@
       <c r="I56" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K56" s="9">
+      <c r="K56" s="16">
         <v>175</v>
       </c>
       <c r="M56" s="3">
@@ -5973,7 +5985,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -5989,7 +6001,7 @@
       <c r="I57" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K57" s="9">
+      <c r="K57" s="16">
         <v>175</v>
       </c>
       <c r="M57" s="3">
@@ -6011,7 +6023,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6027,7 +6039,7 @@
       <c r="I58" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K58" s="9">
+      <c r="K58" s="16">
         <v>176</v>
       </c>
       <c r="M58" s="3">
@@ -6049,7 +6061,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6065,7 +6077,7 @@
       <c r="I59" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K59" s="9">
+      <c r="K59" s="16">
         <v>176</v>
       </c>
       <c r="M59" s="3">
@@ -6087,7 +6099,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6103,7 +6115,7 @@
       <c r="I60" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K60" s="9">
+      <c r="K60" s="16">
         <v>176</v>
       </c>
       <c r="M60" s="3">
@@ -6125,7 +6137,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6141,7 +6153,7 @@
       <c r="I61" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K61" s="9">
+      <c r="K61" s="16">
         <v>176</v>
       </c>
       <c r="M61" s="3">
@@ -6163,7 +6175,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -6179,7 +6191,7 @@
       <c r="I62" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K62" s="9">
+      <c r="K62" s="16">
         <v>176</v>
       </c>
       <c r="M62" s="3">
@@ -6201,7 +6213,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -6217,7 +6229,7 @@
       <c r="I63" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K63" s="9">
+      <c r="K63" s="16">
         <v>176</v>
       </c>
       <c r="M63" s="3">
@@ -6239,7 +6251,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -6255,7 +6267,7 @@
       <c r="I64" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K64" s="9">
+      <c r="K64" s="16">
         <v>176</v>
       </c>
       <c r="M64" s="3">
@@ -6277,7 +6289,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -6293,7 +6305,7 @@
       <c r="I65" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K65" s="9">
+      <c r="K65" s="16">
         <v>176</v>
       </c>
       <c r="M65" s="3">
@@ -6315,7 +6327,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -6331,7 +6343,7 @@
       <c r="I66" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K66" s="9">
+      <c r="K66" s="16">
         <v>176</v>
       </c>
       <c r="M66" s="3">
@@ -6353,7 +6365,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -6369,7 +6381,7 @@
       <c r="I67" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K67" s="9">
+      <c r="K67" s="16">
         <v>177</v>
       </c>
       <c r="M67" s="3">
@@ -6391,7 +6403,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -6407,7 +6419,7 @@
       <c r="I68" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K68" s="9">
+      <c r="K68" s="16">
         <v>177</v>
       </c>
       <c r="M68" s="3">
@@ -6429,7 +6441,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6445,7 +6457,7 @@
       <c r="I69" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K69" s="9">
+      <c r="K69" s="16">
         <v>177</v>
       </c>
       <c r="M69" s="3">
@@ -6467,7 +6479,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6483,7 +6495,7 @@
       <c r="I70" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K70" s="9">
+      <c r="K70" s="16">
         <v>177</v>
       </c>
       <c r="M70" s="3">
@@ -6505,7 +6517,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6521,7 +6533,7 @@
       <c r="I71" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K71" s="9">
+      <c r="K71" s="16">
         <v>177</v>
       </c>
       <c r="M71" s="3">
@@ -6543,7 +6555,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6559,7 +6571,7 @@
       <c r="I72" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K72" s="9">
+      <c r="K72" s="16">
         <v>178</v>
       </c>
       <c r="M72" s="3">
@@ -6581,7 +6593,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -6597,7 +6609,7 @@
       <c r="I73" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K73" s="9">
+      <c r="K73" s="16">
         <v>178</v>
       </c>
       <c r="M73" s="3">
@@ -6619,7 +6631,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6635,7 +6647,7 @@
       <c r="I74" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K74" s="9">
+      <c r="K74" s="16">
         <v>178</v>
       </c>
       <c r="M74" s="3">
@@ -6657,7 +6669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -6673,7 +6685,7 @@
       <c r="I75" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K75" s="9">
+      <c r="K75" s="16">
         <v>180</v>
       </c>
       <c r="M75" s="3">
@@ -6695,7 +6707,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -6711,7 +6723,7 @@
       <c r="I76" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K76" s="9">
+      <c r="K76" s="16">
         <v>180</v>
       </c>
       <c r="M76" s="3">
@@ -6733,7 +6745,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -6749,7 +6761,7 @@
       <c r="I77" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K77" s="9">
+      <c r="K77" s="16">
         <v>182</v>
       </c>
       <c r="M77" s="3">
@@ -6771,7 +6783,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -6787,7 +6799,7 @@
       <c r="I78" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K78" s="9">
+      <c r="K78" s="16">
         <v>182</v>
       </c>
       <c r="M78" s="3">
@@ -6809,7 +6821,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -6825,7 +6837,7 @@
       <c r="I79" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K79" s="9">
+      <c r="K79" s="16">
         <v>182</v>
       </c>
       <c r="M79" s="3">
@@ -6847,7 +6859,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -6863,7 +6875,7 @@
       <c r="I80" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K80" s="9">
+      <c r="K80" s="16">
         <v>183</v>
       </c>
       <c r="M80" s="3">
@@ -6885,7 +6897,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -6901,7 +6913,7 @@
       <c r="I81" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K81" s="9">
+      <c r="K81" s="16">
         <v>183</v>
       </c>
       <c r="M81" s="3">
@@ -6923,7 +6935,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -6939,8 +6951,8 @@
       <c r="I82" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K82" s="9">
-        <v>183</v>
+      <c r="K82" s="16">
+        <v>184</v>
       </c>
       <c r="M82" s="3">
         <v>22</v>
@@ -6961,7 +6973,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -6977,8 +6989,8 @@
       <c r="I83" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K83" s="9">
-        <v>184</v>
+      <c r="K83" s="16">
+        <v>185</v>
       </c>
       <c r="M83" s="3">
         <v>22</v>
@@ -6999,7 +7011,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -7015,7 +7027,7 @@
       <c r="I84" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K84" s="9">
+      <c r="K84" s="16">
         <v>185</v>
       </c>
       <c r="M84" s="3">
@@ -7037,7 +7049,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -7053,8 +7065,8 @@
       <c r="I85" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K85" s="9">
-        <v>185</v>
+      <c r="K85" s="16">
+        <v>186</v>
       </c>
       <c r="M85" s="3">
         <v>22</v>
@@ -7075,7 +7087,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -7091,8 +7103,8 @@
       <c r="I86" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K86" s="9">
-        <v>186</v>
+      <c r="K86" s="16">
+        <v>187</v>
       </c>
       <c r="M86" s="3">
         <v>23</v>
@@ -7113,7 +7125,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -7129,8 +7141,8 @@
       <c r="I87" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K87" s="9">
-        <v>187</v>
+      <c r="K87" s="16">
+        <v>188</v>
       </c>
       <c r="M87" s="3">
         <v>24</v>
@@ -7151,7 +7163,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -7167,8 +7179,8 @@
       <c r="I88" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K88" s="9">
-        <v>188</v>
+      <c r="K88" s="16">
+        <v>190</v>
       </c>
       <c r="M88" s="3">
         <v>24</v>
@@ -7189,7 +7201,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -7205,7 +7217,7 @@
       <c r="I89" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K89" s="9">
+      <c r="K89" s="16">
         <v>190</v>
       </c>
       <c r="M89" s="3">
@@ -7227,7 +7239,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="90" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -7243,8 +7255,8 @@
       <c r="I90" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K90" s="9">
-        <v>190</v>
+      <c r="K90" s="16">
+        <v>194</v>
       </c>
       <c r="M90" s="3">
         <v>26</v>
@@ -7265,7 +7277,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="91" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -7281,8 +7293,8 @@
       <c r="I91" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K91" s="9">
-        <v>194</v>
+      <c r="K91" s="16">
+        <v>195</v>
       </c>
       <c r="M91" s="3">
         <v>30</v>
@@ -7303,7 +7315,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="92" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -7319,14 +7331,14 @@
       <c r="I92" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="K92" s="10">
-        <v>195</v>
+      <c r="K92" s="17">
+        <v>197</v>
       </c>
       <c r="M92" s="4">
         <v>38</v>
       </c>
       <c r="O92" s="10">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="R92" s="7" t="s">
         <v>52</v>

--- a/data/dados-turmas-2026.xlsx
+++ b/data/dados-turmas-2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\estatinfo\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\estatinfo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E748E079-D148-46D1-811B-6B51FA9E7660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED7635AA-3085-46F6-A7B4-BC7710DA9798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="3" r:id="rId1"/>
@@ -155,18 +155,6 @@
     <t>Corinthians</t>
   </si>
   <si>
-    <t>1 a 2 h_sem</t>
-  </si>
-  <si>
-    <t>2 a 2 h_sem</t>
-  </si>
-  <si>
-    <t>3 a 5 h_sem</t>
-  </si>
-  <si>
-    <t>mais de 5 h_sem</t>
-  </si>
-  <si>
     <t>Mais que social</t>
   </si>
   <si>
@@ -176,16 +164,28 @@
     <t>estudo</t>
   </si>
   <si>
-    <t>até 20 h</t>
-  </si>
-  <si>
-    <t>mais 20 h</t>
-  </si>
-  <si>
     <t>atividade_fisica</t>
   </si>
   <si>
     <t>consumo_alcool</t>
+  </si>
+  <si>
+    <t>Outro</t>
+  </si>
+  <si>
+    <t>1_2h_sem</t>
+  </si>
+  <si>
+    <t>3_5h_sem</t>
+  </si>
+  <si>
+    <t>mais_5h_sem</t>
+  </si>
+  <si>
+    <t>ate_20h_sem</t>
+  </si>
+  <si>
+    <t>mais_20h_sem</t>
   </si>
 </sst>
 </file>
@@ -305,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -324,6 +324,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3833,7 +3834,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67291CED-4854-4A07-9C00-39F7F3C0BA26}">
-  <dimension ref="A1:X92"/>
+  <dimension ref="A1:W92"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -3843,24 +3844,24 @@
     <col min="6" max="6" width="3" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="3" customWidth="1"/>
-    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" customWidth="1"/>
     <col min="10" max="10" width="3" customWidth="1"/>
     <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="3" customWidth="1"/>
     <col min="13" max="13" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="3" customWidth="1"/>
     <col min="15" max="15" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="3" customWidth="1"/>
-    <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3" customWidth="1"/>
-    <col min="20" max="20" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3" customWidth="1"/>
-    <col min="22" max="22" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.42578125" customWidth="1"/>
-    <col min="24" max="24" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3" customWidth="1"/>
+    <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3" customWidth="1"/>
+    <col min="19" max="19" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="3" customWidth="1"/>
+    <col min="21" max="21" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.42578125" customWidth="1"/>
+    <col min="23" max="23" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C1" s="12" t="s">
         <v>28</v>
       </c>
@@ -3880,22 +3881,22 @@
         <v>33</v>
       </c>
       <c r="O1" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="R1" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q1" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="S1" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="V1" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="X1" s="12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U1" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="W1" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3920,20 +3921,20 @@
       <c r="O2" s="8">
         <v>0</v>
       </c>
-      <c r="R2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="T2" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="V2" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="U2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="W2" s="18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3958,20 +3959,20 @@
       <c r="O3" s="9">
         <v>1</v>
       </c>
-      <c r="R3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T3" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V3" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X3" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W3" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3996,20 +3997,20 @@
       <c r="O4" s="9">
         <v>1</v>
       </c>
-      <c r="R4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T4" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X4" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U4" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W4" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4034,20 +4035,20 @@
       <c r="O5" s="9">
         <v>2</v>
       </c>
-      <c r="R5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T5" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X5" s="13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S5" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U5" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W5" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4072,20 +4073,20 @@
       <c r="O6" s="9">
         <v>2</v>
       </c>
-      <c r="R6" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T6" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X6" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S6" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U6" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W6" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4110,20 +4111,20 @@
       <c r="O7" s="9">
         <v>2</v>
       </c>
-      <c r="R7" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T7" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X7" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q7" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U7" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W7" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4148,20 +4149,20 @@
       <c r="O8" s="9">
         <v>2</v>
       </c>
-      <c r="R8" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T8" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V8" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X8" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S8" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W8" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4186,20 +4187,20 @@
       <c r="O9" s="9">
         <v>2</v>
       </c>
-      <c r="R9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T9" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X9" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W9" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4224,20 +4225,20 @@
       <c r="O10" s="9">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T10" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X10" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U10" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W10" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4262,20 +4263,20 @@
       <c r="O11" s="9">
         <v>2</v>
       </c>
-      <c r="R11" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T11" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X11" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S11" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U11" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W11" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4300,20 +4301,20 @@
       <c r="O12" s="9">
         <v>2</v>
       </c>
-      <c r="R12" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T12" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V12" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X12" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q12" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S12" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W12" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4338,20 +4339,20 @@
       <c r="O13" s="9">
         <v>3</v>
       </c>
-      <c r="R13" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T13" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X13" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S13" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U13" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W13" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4376,20 +4377,20 @@
       <c r="O14" s="9">
         <v>3</v>
       </c>
-      <c r="R14" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X14" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q14" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W14" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4414,20 +4415,20 @@
       <c r="O15" s="9">
         <v>3</v>
       </c>
-      <c r="R15" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T15" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X15" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S15" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U15" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W15" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4452,20 +4453,20 @@
       <c r="O16" s="9">
         <v>3</v>
       </c>
-      <c r="R16" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T16" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V16" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X16" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q16" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U16" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W16" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4490,20 +4491,20 @@
       <c r="O17" s="9">
         <v>3</v>
       </c>
-      <c r="R17" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T17" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X17" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q17" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U17" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W17" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4516,8 +4517,8 @@
       <c r="G18" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>25</v>
+      <c r="I18" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="K18" s="16">
         <v>163</v>
@@ -4528,20 +4529,20 @@
       <c r="O18" s="9">
         <v>3</v>
       </c>
-      <c r="R18" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T18" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X18" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q18" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U18" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W18" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4554,8 +4555,8 @@
       <c r="G19" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>25</v>
+      <c r="I19" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="K19" s="16">
         <v>163</v>
@@ -4566,20 +4567,20 @@
       <c r="O19" s="9">
         <v>3</v>
       </c>
-      <c r="R19" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T19" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V19" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X19" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q19" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S19" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U19" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="W19" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4604,20 +4605,20 @@
       <c r="O20" s="9">
         <v>3</v>
       </c>
-      <c r="R20" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T20" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V20" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="X20" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q20" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S20" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U20" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W20" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4642,20 +4643,20 @@
       <c r="O21" s="9">
         <v>3</v>
       </c>
-      <c r="R21" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T21" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V21" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="X21" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q21" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W21" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4680,20 +4681,20 @@
       <c r="O22" s="9">
         <v>3</v>
       </c>
-      <c r="R22" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T22" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V22" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="X22" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q22" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S22" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U22" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W22" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4718,20 +4719,20 @@
       <c r="O23" s="9">
         <v>3</v>
       </c>
-      <c r="R23" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V23" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="X23" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q23" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S23" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U23" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W23" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4756,20 +4757,20 @@
       <c r="O24" s="9">
         <v>3</v>
       </c>
-      <c r="R24" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V24" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="X24" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q24" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S24" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U24" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W24" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4794,20 +4795,20 @@
       <c r="O25" s="9">
         <v>4</v>
       </c>
-      <c r="R25" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T25" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V25" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="X25" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q25" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S25" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U25" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W25" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4832,20 +4833,20 @@
       <c r="O26" s="9">
         <v>4</v>
       </c>
-      <c r="R26" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T26" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V26" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="X26" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q26" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S26" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U26" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W26" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4870,20 +4871,20 @@
       <c r="O27" s="9">
         <v>4</v>
       </c>
-      <c r="R27" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T27" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V27" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="X27" s="9" t="s">
+      <c r="Q27" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S27" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U27" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W27" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4908,20 +4909,20 @@
       <c r="O28" s="9">
         <v>4</v>
       </c>
-      <c r="R28" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T28" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V28" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="X28" s="9" t="s">
+      <c r="Q28" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S28" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U28" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W28" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4946,20 +4947,20 @@
       <c r="O29" s="9">
         <v>4</v>
       </c>
-      <c r="R29" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T29" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V29" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="X29" s="9" t="s">
+      <c r="Q29" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S29" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U29" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W29" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4984,20 +4985,20 @@
       <c r="O30" s="9">
         <v>4</v>
       </c>
-      <c r="R30" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T30" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V30" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="X30" s="9" t="s">
+      <c r="Q30" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S30" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U30" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W30" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5022,20 +5023,20 @@
       <c r="O31" s="9">
         <v>4</v>
       </c>
-      <c r="R31" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T31" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V31" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="X31" s="9" t="s">
+      <c r="Q31" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S31" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U31" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W31" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5060,20 +5061,20 @@
       <c r="O32" s="9">
         <v>4</v>
       </c>
-      <c r="R32" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T32" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V32" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="X32" s="9" t="s">
+      <c r="Q32" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S32" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U32" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W32" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5098,20 +5099,20 @@
       <c r="O33" s="9">
         <v>4</v>
       </c>
-      <c r="R33" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T33" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V33" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="X33" s="9" t="s">
+      <c r="Q33" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S33" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U33" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W33" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5136,20 +5137,20 @@
       <c r="O34" s="9">
         <v>5</v>
       </c>
-      <c r="R34" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T34" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V34" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="X34" s="9" t="s">
+      <c r="Q34" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S34" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U34" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W34" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5174,20 +5175,20 @@
       <c r="O35" s="9">
         <v>5</v>
       </c>
-      <c r="R35" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T35" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V35" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="X35" s="9" t="s">
+      <c r="Q35" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S35" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U35" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W35" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5212,20 +5213,20 @@
       <c r="O36" s="9">
         <v>5</v>
       </c>
-      <c r="R36" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T36" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V36" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="X36" s="9" t="s">
+      <c r="Q36" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S36" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U36" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W36" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5250,20 +5251,20 @@
       <c r="O37" s="9">
         <v>5</v>
       </c>
-      <c r="R37" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T37" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V37" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="X37" s="9" t="s">
+      <c r="Q37" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S37" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U37" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W37" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5288,20 +5289,20 @@
       <c r="O38" s="9">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T38" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V38" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="X38" s="9" t="s">
+      <c r="Q38" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S38" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U38" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="W38" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5326,20 +5327,20 @@
       <c r="O39" s="9">
         <v>5</v>
       </c>
-      <c r="R39" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T39" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V39" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="X39" s="9" t="s">
+      <c r="Q39" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S39" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U39" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W39" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5364,20 +5365,20 @@
       <c r="O40" s="9">
         <v>5</v>
       </c>
-      <c r="R40" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T40" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V40" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X40" s="9" t="s">
+      <c r="Q40" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S40" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U40" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W40" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5402,20 +5403,20 @@
       <c r="O41" s="9">
         <v>5</v>
       </c>
-      <c r="R41" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T41" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V41" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X41" s="9" t="s">
+      <c r="Q41" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S41" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U41" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W41" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5440,20 +5441,20 @@
       <c r="O42" s="9">
         <v>5</v>
       </c>
-      <c r="R42" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T42" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V42" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X42" s="9" t="s">
+      <c r="Q42" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S42" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U42" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W42" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5478,20 +5479,20 @@
       <c r="O43" s="9">
         <v>5</v>
       </c>
-      <c r="R43" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T43" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V43" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X43" s="9" t="s">
+      <c r="Q43" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S43" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U43" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W43" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5516,20 +5517,20 @@
       <c r="O44" s="9">
         <v>6</v>
       </c>
-      <c r="R44" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T44" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V44" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X44" s="9" t="s">
+      <c r="Q44" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S44" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U44" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W44" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5554,20 +5555,20 @@
       <c r="O45" s="9">
         <v>6</v>
       </c>
-      <c r="R45" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T45" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V45" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X45" s="9" t="s">
+      <c r="Q45" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S45" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U45" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W45" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5592,20 +5593,20 @@
       <c r="O46" s="9">
         <v>6</v>
       </c>
-      <c r="R46" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T46" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V46" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X46" s="9" t="s">
+      <c r="Q46" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S46" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U46" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W46" s="13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5630,20 +5631,20 @@
       <c r="O47" s="9">
         <v>6</v>
       </c>
-      <c r="R47" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T47" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V47" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X47" s="9" t="s">
+      <c r="Q47" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S47" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U47" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W47" s="13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5668,20 +5669,20 @@
       <c r="O48" s="9">
         <v>6</v>
       </c>
-      <c r="R48" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T48" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V48" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X48" s="9" t="s">
+      <c r="Q48" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S48" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U48" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W48" s="13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5706,20 +5707,20 @@
       <c r="O49" s="9">
         <v>6</v>
       </c>
-      <c r="R49" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T49" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V49" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X49" s="9" t="s">
+      <c r="Q49" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S49" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U49" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W49" s="13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5744,20 +5745,20 @@
       <c r="O50" s="9">
         <v>6</v>
       </c>
-      <c r="R50" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T50" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V50" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X50" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Q50" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S50" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U50" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W50" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5782,20 +5783,20 @@
       <c r="O51" s="9">
         <v>6</v>
       </c>
-      <c r="R51" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T51" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V51" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X51" s="9" t="s">
+      <c r="Q51" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S51" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U51" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W51" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5820,20 +5821,20 @@
       <c r="O52" s="9">
         <v>6</v>
       </c>
-      <c r="R52" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T52" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V52" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X52" s="9" t="s">
+      <c r="Q52" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S52" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U52" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W52" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5858,20 +5859,20 @@
       <c r="O53" s="9">
         <v>6</v>
       </c>
-      <c r="R53" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T53" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V53" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X53" s="9" t="s">
+      <c r="Q53" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S53" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U53" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W53" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5896,20 +5897,20 @@
       <c r="O54" s="9">
         <v>6</v>
       </c>
-      <c r="R54" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T54" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V54" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X54" s="9" t="s">
+      <c r="Q54" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S54" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U54" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W54" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5934,20 +5935,20 @@
       <c r="O55" s="9">
         <v>7</v>
       </c>
-      <c r="R55" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T55" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V55" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X55" s="9" t="s">
+      <c r="Q55" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S55" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U55" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W55" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5972,20 +5973,20 @@
       <c r="O56" s="9">
         <v>7</v>
       </c>
-      <c r="R56" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T56" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V56" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X56" s="9" t="s">
+      <c r="Q56" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S56" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U56" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W56" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6010,20 +6011,20 @@
       <c r="O57" s="9">
         <v>8</v>
       </c>
-      <c r="R57" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T57" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V57" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X57" s="9" t="s">
+      <c r="Q57" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S57" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U57" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W57" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6048,20 +6049,20 @@
       <c r="O58" s="9">
         <v>8</v>
       </c>
-      <c r="R58" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T58" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V58" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X58" s="9" t="s">
+      <c r="Q58" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S58" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U58" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W58" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6086,20 +6087,20 @@
       <c r="O59" s="9">
         <v>8</v>
       </c>
-      <c r="R59" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T59" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V59" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X59" s="9" t="s">
+      <c r="Q59" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S59" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U59" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W59" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6124,20 +6125,20 @@
       <c r="O60" s="9">
         <v>8</v>
       </c>
-      <c r="R60" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T60" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V60" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X60" s="9" t="s">
+      <c r="Q60" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S60" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U60" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W60" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6162,20 +6163,20 @@
       <c r="O61" s="9">
         <v>8</v>
       </c>
-      <c r="R61" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T61" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V61" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X61" s="9" t="s">
+      <c r="Q61" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S61" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U61" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W61" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -6186,7 +6187,7 @@
         <v>1</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I62" s="6" t="s">
         <v>42</v>
@@ -6200,20 +6201,20 @@
       <c r="O62" s="9">
         <v>8</v>
       </c>
-      <c r="R62" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T62" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V62" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X62" s="9" t="s">
+      <c r="Q62" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S62" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U62" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W62" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -6238,20 +6239,20 @@
       <c r="O63" s="9">
         <v>8</v>
       </c>
-      <c r="R63" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T63" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V63" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X63" s="9" t="s">
+      <c r="Q63" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S63" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U63" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W63" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -6276,20 +6277,20 @@
       <c r="O64" s="9">
         <v>8</v>
       </c>
-      <c r="R64" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T64" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V64" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X64" s="9" t="s">
+      <c r="Q64" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S64" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U64" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W64" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -6303,7 +6304,7 @@
         <v>8</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K65" s="16">
         <v>176</v>
@@ -6314,20 +6315,20 @@
       <c r="O65" s="9">
         <v>9</v>
       </c>
-      <c r="R65" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T65" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V65" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X65" s="9" t="s">
+      <c r="Q65" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S65" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U65" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W65" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -6352,20 +6353,20 @@
       <c r="O66" s="9">
         <v>9</v>
       </c>
-      <c r="R66" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T66" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V66" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X66" s="9" t="s">
+      <c r="Q66" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S66" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U66" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W66" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -6390,20 +6391,20 @@
       <c r="O67" s="9">
         <v>10</v>
       </c>
-      <c r="R67" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T67" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V67" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X67" s="9" t="s">
+      <c r="Q67" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S67" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U67" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W67" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -6428,20 +6429,20 @@
       <c r="O68" s="9">
         <v>10</v>
       </c>
-      <c r="R68" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="T68" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V68" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X68" s="9" t="s">
+      <c r="Q68" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="S68" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U68" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W68" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6466,20 +6467,20 @@
       <c r="O69" s="9">
         <v>10</v>
       </c>
-      <c r="R69" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="T69" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V69" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X69" s="9" t="s">
+      <c r="Q69" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S69" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U69" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W69" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6504,20 +6505,20 @@
       <c r="O70" s="9">
         <v>10</v>
       </c>
-      <c r="R70" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="T70" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V70" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X70" s="9" t="s">
+      <c r="Q70" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="S70" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U70" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W70" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6542,20 +6543,20 @@
       <c r="O71" s="9">
         <v>10</v>
       </c>
-      <c r="R71" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="T71" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V71" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X71" s="9" t="s">
+      <c r="Q71" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="S71" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U71" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W71" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6580,20 +6581,20 @@
       <c r="O72" s="9">
         <v>10</v>
       </c>
-      <c r="R72" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="T72" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V72" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X72" s="9" t="s">
+      <c r="Q72" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="S72" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U72" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W72" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -6618,20 +6619,20 @@
       <c r="O73" s="9">
         <v>10</v>
       </c>
-      <c r="R73" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="T73" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V73" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X73" s="9" t="s">
+      <c r="Q73" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="S73" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="U73" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="W73" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6642,7 +6643,7 @@
         <v>1</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I74" s="6" t="s">
         <v>43</v>
@@ -6656,20 +6657,20 @@
       <c r="O74" s="9">
         <v>10</v>
       </c>
-      <c r="R74" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="T74" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="V74" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X74" s="9" t="s">
+      <c r="Q74" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="S74" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="U74" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W74" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -6694,20 +6695,20 @@
       <c r="O75" s="9">
         <v>10</v>
       </c>
-      <c r="R75" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="T75" s="9" t="s">
+      <c r="Q75" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="S75" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="V75" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="X75" s="9" t="s">
+      <c r="U75" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W75" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -6732,20 +6733,20 @@
       <c r="O76" s="9">
         <v>10</v>
       </c>
-      <c r="R76" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="T76" s="9" t="s">
+      <c r="Q76" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S76" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="V76" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="X76" s="9" t="s">
+      <c r="U76" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W76" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -6770,20 +6771,20 @@
       <c r="O77" s="9">
         <v>10</v>
       </c>
-      <c r="R77" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="T77" s="9" t="s">
+      <c r="Q77" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S77" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="V77" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="X77" s="9" t="s">
+      <c r="U77" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W77" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -6808,20 +6809,20 @@
       <c r="O78" s="9">
         <v>10</v>
       </c>
-      <c r="R78" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="T78" s="9" t="s">
+      <c r="Q78" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S78" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="V78" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="X78" s="9" t="s">
+      <c r="U78" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W78" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -6846,20 +6847,20 @@
       <c r="O79" s="9">
         <v>11</v>
       </c>
-      <c r="R79" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="T79" s="9" t="s">
+      <c r="Q79" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S79" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="V79" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="X79" s="9" t="s">
+      <c r="U79" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W79" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -6884,20 +6885,20 @@
       <c r="O80" s="9">
         <v>12</v>
       </c>
-      <c r="R80" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="T80" s="9" t="s">
+      <c r="Q80" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S80" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="V80" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="X80" s="9" t="s">
+      <c r="U80" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W80" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -6922,20 +6923,20 @@
       <c r="O81" s="9">
         <v>12</v>
       </c>
-      <c r="R81" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="T81" s="9" t="s">
+      <c r="Q81" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S81" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="V81" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="X81" s="9" t="s">
+      <c r="U81" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W81" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -6960,20 +6961,20 @@
       <c r="O82" s="9">
         <v>12</v>
       </c>
-      <c r="R82" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="T82" s="9" t="s">
+      <c r="Q82" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S82" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="V82" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="X82" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="83" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U82" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W82" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -6998,20 +6999,20 @@
       <c r="O83" s="9">
         <v>12</v>
       </c>
-      <c r="R83" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="T83" s="9" t="s">
+      <c r="Q83" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S83" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="V83" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="X83" s="13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="84" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U83" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W83" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -7036,20 +7037,20 @@
       <c r="O84" s="9">
         <v>12</v>
       </c>
-      <c r="R84" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="T84" s="9" t="s">
+      <c r="Q84" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S84" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="V84" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="X84" s="13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="85" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U84" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W84" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -7074,20 +7075,20 @@
       <c r="O85" s="9">
         <v>14</v>
       </c>
-      <c r="R85" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="T85" s="9" t="s">
+      <c r="Q85" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S85" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="V85" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="X85" s="13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U85" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W85" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -7112,20 +7113,20 @@
       <c r="O86" s="9">
         <v>15</v>
       </c>
-      <c r="R86" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="T86" s="9" t="s">
+      <c r="Q86" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S86" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="V86" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="X86" s="13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="87" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U86" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W86" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -7150,20 +7151,20 @@
       <c r="O87" s="9">
         <v>15</v>
       </c>
-      <c r="R87" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="T87" s="9" t="s">
+      <c r="Q87" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S87" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="V87" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="X87" s="13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="88" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U87" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W87" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -7188,20 +7189,20 @@
       <c r="O88" s="9">
         <v>15</v>
       </c>
-      <c r="R88" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="T88" s="9" t="s">
+      <c r="Q88" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S88" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="V88" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="X88" s="13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="89" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U88" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W88" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -7226,20 +7227,20 @@
       <c r="O89" s="9">
         <v>16</v>
       </c>
-      <c r="R89" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="T89" s="9" t="s">
+      <c r="Q89" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S89" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="V89" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="X89" s="13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="90" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U89" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W89" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -7264,20 +7265,20 @@
       <c r="O90" s="9">
         <v>18</v>
       </c>
-      <c r="R90" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="T90" s="9" t="s">
+      <c r="Q90" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S90" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="V90" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="X90" s="13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="91" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U90" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W90" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -7302,20 +7303,20 @@
       <c r="O91" s="9">
         <v>20</v>
       </c>
-      <c r="R91" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="T91" s="9" t="s">
+      <c r="Q91" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="S91" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="V91" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="X91" s="13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="92" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="U91" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="W91" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -7340,22 +7341,22 @@
       <c r="O92" s="10">
         <v>30</v>
       </c>
-      <c r="R92" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="T92" s="10" t="s">
+      <c r="Q92" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="S92" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="V92" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="X92" s="14" t="s">
-        <v>48</v>
+      <c r="U92" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="W92" s="14" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="X2:X102">
-    <sortCondition ref="X2:X102"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="W2:W92">
+    <sortCondition ref="W2:W92"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.39370078740157483" right="0.11811023622047245" top="0.39370078740157483" bottom="0.39370078740157483" header="0.11811023622047245" footer="0.11811023622047245"/>

--- a/data/dados-turmas-2026.xlsx
+++ b/data/dados-turmas-2026.xlsx
@@ -8,15 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\estatinfo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED7635AA-3085-46F6-A7B4-BC7710DA9798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80EB0E2A-A03C-4A65-8762-212218F814F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="3" r:id="rId1"/>
     <sheet name="Planilha2" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -589,22 +602,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D60CCD58-E5F4-4C6F-A78C-39DF9E1D4064}">
   <dimension ref="A1:K92"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="34" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.88671875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
@@ -639,7 +652,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -674,7 +687,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -709,7 +722,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -744,7 +757,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -779,7 +792,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -814,7 +827,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -849,7 +862,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -884,7 +897,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -919,7 +932,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -954,7 +967,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -989,7 +1002,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -1024,7 +1037,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -1059,7 +1072,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -1094,7 +1107,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -1129,7 +1142,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>0</v>
       </c>
@@ -1164,7 +1177,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -1199,7 +1212,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>0</v>
       </c>
@@ -1234,7 +1247,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -1269,7 +1282,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -1304,7 +1317,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -1339,7 +1352,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>0</v>
       </c>
@@ -1374,7 +1387,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>0</v>
       </c>
@@ -1409,7 +1422,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -1444,7 +1457,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>0</v>
       </c>
@@ -1479,7 +1492,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -1514,7 +1527,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -1549,7 +1562,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>0</v>
       </c>
@@ -1584,7 +1597,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>27</v>
       </c>
@@ -1619,7 +1632,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>0</v>
       </c>
@@ -1654,7 +1667,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>0</v>
       </c>
@@ -1689,7 +1702,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>0</v>
       </c>
@@ -1724,7 +1737,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>27</v>
       </c>
@@ -1759,7 +1772,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>0</v>
       </c>
@@ -1794,7 +1807,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -1829,7 +1842,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>27</v>
       </c>
@@ -1864,7 +1877,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>0</v>
       </c>
@@ -1899,7 +1912,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>0</v>
       </c>
@@ -1934,7 +1947,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>0</v>
       </c>
@@ -1969,7 +1982,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -2004,7 +2017,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>0</v>
       </c>
@@ -2039,7 +2052,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>0</v>
       </c>
@@ -2074,7 +2087,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>27</v>
       </c>
@@ -2109,7 +2122,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>0</v>
       </c>
@@ -2144,7 +2157,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>27</v>
       </c>
@@ -2179,7 +2192,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>0</v>
       </c>
@@ -2214,7 +2227,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>0</v>
       </c>
@@ -2249,7 +2262,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>0</v>
       </c>
@@ -2284,7 +2297,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>0</v>
       </c>
@@ -2319,7 +2332,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>27</v>
       </c>
@@ -2354,7 +2367,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>0</v>
       </c>
@@ -2389,7 +2402,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>0</v>
       </c>
@@ -2424,7 +2437,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>27</v>
       </c>
@@ -2459,7 +2472,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>27</v>
       </c>
@@ -2494,7 +2507,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>0</v>
       </c>
@@ -2529,7 +2542,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>0</v>
       </c>
@@ -2564,7 +2577,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>0</v>
       </c>
@@ -2599,7 +2612,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>0</v>
       </c>
@@ -2634,7 +2647,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>0</v>
       </c>
@@ -2669,7 +2682,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>27</v>
       </c>
@@ -2704,7 +2717,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>0</v>
       </c>
@@ -2739,7 +2752,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>27</v>
       </c>
@@ -2774,7 +2787,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>0</v>
       </c>
@@ -2809,7 +2822,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>0</v>
       </c>
@@ -2844,7 +2857,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>0</v>
       </c>
@@ -2879,7 +2892,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>0</v>
       </c>
@@ -2914,7 +2927,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>0</v>
       </c>
@@ -2949,7 +2962,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>0</v>
       </c>
@@ -2984,7 +2997,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>0</v>
       </c>
@@ -3019,7 +3032,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>0</v>
       </c>
@@ -3054,7 +3067,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>0</v>
       </c>
@@ -3089,7 +3102,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>27</v>
       </c>
@@ -3124,7 +3137,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>0</v>
       </c>
@@ -3159,7 +3172,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>0</v>
       </c>
@@ -3194,7 +3207,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>27</v>
       </c>
@@ -3229,7 +3242,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>27</v>
       </c>
@@ -3264,7 +3277,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>0</v>
       </c>
@@ -3299,7 +3312,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>0</v>
       </c>
@@ -3334,7 +3347,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>0</v>
       </c>
@@ -3369,7 +3382,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>0</v>
       </c>
@@ -3404,7 +3417,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>0</v>
       </c>
@@ -3439,7 +3452,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>27</v>
       </c>
@@ -3474,7 +3487,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>0</v>
       </c>
@@ -3509,7 +3522,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>27</v>
       </c>
@@ -3544,7 +3557,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>0</v>
       </c>
@@ -3579,7 +3592,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>0</v>
       </c>
@@ -3614,7 +3627,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>0</v>
       </c>
@@ -3649,7 +3662,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>27</v>
       </c>
@@ -3684,7 +3697,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>27</v>
       </c>
@@ -3719,7 +3732,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>0</v>
       </c>
@@ -3754,7 +3767,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>0</v>
       </c>
@@ -3789,7 +3802,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>27</v>
       </c>
@@ -3835,33 +3848,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67291CED-4854-4A07-9C00-39F7F3C0BA26}">
   <dimension ref="A1:W92"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="1.85546875" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="1.88671875" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="6" max="6" width="3" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="3" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" customWidth="1"/>
     <col min="10" max="10" width="3" customWidth="1"/>
     <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="3" customWidth="1"/>
-    <col min="13" max="13" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.44140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="3" customWidth="1"/>
-    <col min="15" max="15" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="3" customWidth="1"/>
     <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="3" customWidth="1"/>
-    <col min="19" max="19" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3" customWidth="1"/>
-    <col min="21" max="21" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.42578125" customWidth="1"/>
-    <col min="23" max="23" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.44140625" customWidth="1"/>
+    <col min="23" max="23" width="15.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="11" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C1" s="12" t="s">
         <v>28</v>
       </c>
@@ -3896,7 +3909,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3934,7 +3947,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3972,7 +3985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4010,7 +4023,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4048,7 +4061,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4086,7 +4099,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4124,7 +4137,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4162,7 +4175,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4200,7 +4213,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4238,7 +4251,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4276,7 +4289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4314,7 +4327,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4352,7 +4365,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4390,7 +4403,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4428,7 +4441,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4466,7 +4479,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4504,7 +4517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4542,7 +4555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4580,7 +4593,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4618,7 +4631,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4656,7 +4669,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4694,7 +4707,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4732,7 +4745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4770,7 +4783,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4808,7 +4821,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4846,7 +4859,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4884,7 +4897,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4922,7 +4935,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4960,7 +4973,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4998,7 +5011,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5036,7 +5049,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5074,7 +5087,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5112,7 +5125,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5150,7 +5163,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5188,7 +5201,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5226,7 +5239,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5264,7 +5277,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5302,7 +5315,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5340,7 +5353,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5378,7 +5391,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5416,7 +5429,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5454,7 +5467,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5492,7 +5505,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5530,7 +5543,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5568,7 +5581,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5606,7 +5619,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5644,7 +5657,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5682,7 +5695,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5720,7 +5733,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5758,7 +5771,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5796,7 +5809,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5834,7 +5847,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5872,7 +5885,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5910,7 +5923,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5948,7 +5961,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5986,7 +5999,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6024,7 +6037,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6062,7 +6075,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6100,7 +6113,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6138,7 +6151,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6176,7 +6189,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -6214,7 +6227,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -6252,7 +6265,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -6290,7 +6303,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -6328,7 +6341,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -6366,7 +6379,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -6404,7 +6417,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -6442,7 +6455,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6480,7 +6493,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6518,7 +6531,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6556,7 +6569,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6594,7 +6607,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -6632,7 +6645,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6670,7 +6683,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -6708,7 +6721,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -6746,7 +6759,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -6784,7 +6797,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -6822,7 +6835,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -6860,7 +6873,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -6898,7 +6911,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -6936,7 +6949,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -6974,7 +6987,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -7012,7 +7025,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -7050,7 +7063,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -7088,7 +7101,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -7126,7 +7139,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -7164,7 +7177,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -7202,7 +7215,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -7240,7 +7253,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -7278,7 +7291,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -7316,7 +7329,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
